--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -9,14 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_この資料について" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_区分ごとの件数" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_資料の徴求を要するもの" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_資料が届かない場合の扱い" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_公表資料により確認できるもの" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_ご判断・ご決定を求めるもの" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_資料の徴求を要しないもの" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_優先してご提供をお願いするもの" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_資料提供依頼の台帳" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_自己点検" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_仕様書の業務内容別" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_資料の徴求を要するもの" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_資料が届かない場合の扱い" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_公表資料により確認できるもの" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_ご判断・ご決定を求めるもの" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_資料の徴求を要しないもの" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_優先してご提供をお願いするもの" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_工程から逆算した区分と律速" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_決着した事項とその経緯" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_資料提供依頼の台帳" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_自己点検" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -180,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,6 +223,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -593,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -940,8 +946,257 @@
       <c r="H25" s="12" t="n"/>
     </row>
     <row r="26"/>
-    <row r="27" ht="86" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>4　本資料の構成と、ご覧いただく順序</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>シート</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>何が分かるか</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>01シート</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>区分ごとの件数と、不足している情報の性質</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="12" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>02シート</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>仕様書の業務内容ごとの件数。どの業務にご確認・ご判断が集まっているか</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="12" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>03シート</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>資料の徴求を要するものの明細（出どころ・徴求する資料）</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="12" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>04シート</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>資料が届かない場合の扱いの明細</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="12" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>05シート</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>公表資料により確認できるものの明細</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="12" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>06シート</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>ご判断・ご決定を求めるものの明細（お決めいただくこと）</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="12" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>07シート</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>資料の徴求を要しないものの明細</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="12" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>08シート</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>優先してご提供をお願いする資料</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="12" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>09シート</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>動かせない日程から逆算した区分と、律速</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="12" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>10シート</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>決着した事項と、何により決着したか</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>11シート</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>資料提供依頼の台帳との関係</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>12シート</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>本資料の内容を機械で確かめた結果</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>注　まず01シート（区分ごとの件数）と08シート（優先してご提供をお願いする資料）をご覧いただければ、何をいつまでにご提供いただく必要があるかが分かります。09シートは、動かせない日程ごとに何が必要かを示したものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="86" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>注1　確認事項は189件（うちご決定・ご確認をお待ちしているもの173件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は受託者が仮に置くものであり、決定ではありません。令和8年10月の意見交換会で内容をお諮りします。
@@ -951,27 +1206,41 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="34">
     <mergeCell ref="C8"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="C40:H40"/>
     <mergeCell ref="C7"/>
+    <mergeCell ref="C31:H31"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="D22:H22"/>
+    <mergeCell ref="C36:H36"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="C39:H39"/>
     <mergeCell ref="C6"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C32:H32"/>
+    <mergeCell ref="C38:H38"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C37:H37"/>
     <mergeCell ref="C10"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C34:H34"/>
+    <mergeCell ref="C30:H30"/>
     <mergeCell ref="C9"/>
     <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C33:H33"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="D24:H24"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="D23:H23"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="C29:H29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -983,7 +1252,2631 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>動かせない日程から逆算した区分と、律速</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>確認事項を、動かせない日程（第2次概算・予算編成用・意見公募手続・最終協議・計画の決定）から逆算して区分したものです。あわせて、決着しないと当方の作業が論理的に進められないもの（律速）を示します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　動かせない日程と、その日程が必要とする確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>期日</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>この日程が必要とするもの</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>うち区分A</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>うちご判断</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>月額に効く</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>法第117条</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>令和8年10月30日</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量 第2次概算</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物にサービス見込量・給付費・保険料・第6章を含むもの</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>令和8年11月13日</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量 予算編成用（美瑛町の予算編成に用いる）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>令和9年1月</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>意見公募手続（ウェブで2週間・概要版を用いる）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>既定値によっても計画本文に未確定箇所の記号が残るもの</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>令和9年2月19日</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>事務管理者・主監会議協議（最終協議・原稿及び数値の確定）</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>保険料の月額に効くもの</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>令和9年3月3日</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>計画の決定（データの締切り）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>未決の全件</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>173</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>令和9年3月23日</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>広域連合議会</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>未決の全件</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>173</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>63</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>期日</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>この日までに決着を要する理由</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月30日</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量 第2次概算</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>算定の前提をこの日までに置く。既定値のまま組める</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="12" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>令和8年11月13日</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量 予算編成用（美瑛町の予算編成に用いる）</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>第2次概算と同じ前提による。3町の意見を反映する</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="12" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>令和9年1月</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>意見公募手続（ウェブで2週間・概要版を用いる）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>未確定箇所の記号が残る間は公表に付せない</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="12" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>令和9年2月19日</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>事務管理者・主監会議協議（最終協議・原稿及び数値の確定）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>この日までに数値を確定する</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="12" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>令和9年3月3日</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>計画の決定（データの締切り）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>以後は数値を動かせない</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="12" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>令和9年3月23日</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>広域連合議会</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>計画の報告</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="12" t="n"/>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>注1　日程ごとに数え方が違います。期限の到来だけで数えると、期限が令和8年10月までのものが大半であるため、どの日程でも同じ件数になります。
+注2　いずれの日程も、ご決定を待たずに組めます。未決の全件に「決着しない場合の当方の扱い」を置いているためです。ただし意見公募手続に付す段では、未確定箇所の記号を解消しておく必要があります。
+注3　期日は業務工程管理表の月別工程によります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2　律速（決着しないと当方の作業が進められないもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>見るもの</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="46" customHeight="1">
+      <c r="A23" s="6" t="inlineStr"/>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>決着しない場合の当方の扱いがない確認事項</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>扱いがなければ、決まるまで当該の作業が止まる。未決の全件に扱いを置いているため、作業が止まるものはない</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="46" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>据え置きの区分A（受託者の側で確定できるもの）</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>受託者の側で確定できる据え置きは、令和8年10月1日にすべて確定した。当方の作業だけで進められるものは残っていない</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="46" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>資料が届かないと計画の記載に跡が残るもの</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20件</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>②未確定箇所の記号が残るもの・③当該の記述が残らないもの。公表の前に解消を要する</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="12" t="n"/>
+    </row>
+    <row r="26" ht="70" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>注1　律速は当方の作業の側にはありません。残るのは、資料のご提供と照会という相手のある作業です。このうち計画の記載に跡が残る20件が、公表の前に解消を要するものです。
+注2　本項の20件と、1の意見公募手続の行の15件は数えているものが違います。本項は区分Aのうち扱いが②③であるもの、1の行は区分を問わず既定値によっても未確定箇所の記号が残るものです。扱い③（当該の記載を掲げない）は記号を残さないため1には現れません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>3　相手のある作業（催促・照会を要するもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>お願いする先</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>影響度</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>ご提供をお願いする資料</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>届かない場合の扱い</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="34" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>優先（6点）</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>①　安全側の置き方で算定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="34" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>広域連合・3町</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>優先（8点）</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>④　現に確認できている値で確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>広域連合・3町</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>優先（7点）</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の6事業別の事業費</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>通常（4点）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>④　現に確認できている値で確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>3町・事業者</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>通常（3点）</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>②　未確定箇所として残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>189</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>法令</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>通常（3点）</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>医療法等の一部を改正する法律（令和7年法律第87号）による介護保険法の改正の内容及び施行の日、並びに医療法第30条の18の5の条文</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>②　未確定箇所として残す</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>注　区分A及び区分Bのうち、保険料の月額に効くもの、介護保険法第117条に関わるもの、又は影響度が至急若しくは優先であるものを掲げました（6件）。いずれも催促又は照会により進むものです。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="C17:H17"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="C15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="68" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>決着した確認事項（16件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>決着した確認事項について、何により決着したかを一覧としたものです。同じ問いを二重に起票しないため、及び決着の根拠をたどれるようにするために掲げています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>決着の日付</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>業務内容</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>何により決着したか</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>特別地域加算の対象地域告示</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月15日</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>厚生労働省『介護保険における特別地域加算・中山間地域等小規模事業所加算・中山間地域等居住者サービス提供加算の対象地域一覧』により確認した。特別地域加算の対象地域のうち北海道で対象となるのは全域を範囲とする市町村22及び一部だけを対象とする市町村14であり、構成3町はいずれも掲げられていない。豪雪地帯、特別豪雪地帯、辺地又は過疎地域であることは対象となるための前提の一つであり、厚生労働大臣が別に定める地域として掲げられていなければ対象とならない。…</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>第7期の保険料基準額</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>令和8年7月30日</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>見える化C1（介護保険事業計画報告値）により6,077円を確認した（令和8年7月30日受領）。条例による確認は不要となった。</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>年齢階級別・要介護度別の認定率</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>令和8年7月29日</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>令和8年7月29日にB4a・B4c・B4d・B4e・B5a・B6a・B6bを受領。認定率の年齢調整分析（7シート）として分析済み</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の実績の推定方法</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>令和8年8月26日</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月26日の進捗確認の打合せで了承。対前年比等の単純な外挿は用いない</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>給付実績データに含まれる個人情報の取扱い</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>了承済（保管せず廃棄）</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>令和8年8月28日</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月28日、発注者より「保管せず廃棄する方針」とのご指示をいただいた。受託者は集計シートの値のみを成果品に収録し、個票を含む受領ファイルは作業終了後ただちに消去した。②の保管期間の設定は不要となった。③町別ファイルの第1シートが広域連合の全件である点は、町へお渡しになる場合のご参考として引き続きお伝えする</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>中間報告会議の議事録の記載の確認【回答済】</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>議事録に反映済み。年報・月報の到着後に資料No.21・22を受領済とする</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>62</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>社人研推計の町別データの入手（完了）</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>令和8年8月31日</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月31日に結果表3-1〜3-4をご提供いただき解消した。按分をやめて公表値に置き換えた結果、町別の補正方向が4件変わった（東川町の75歳以上は「上方に補正」から「補正しない」へ、美瑛町の75歳以上は「補正しない」から「上方に補正」へ）。3町計の補正係数と保険料の試算には影響しない</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>71</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>交付金の評価結果を委員会資料として整理したこと</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月3日</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>(2)・(7)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月3日「確認事項2件はともにOKです。進めて下さい。」により①〜③を了承。第3章の節番号の繰り上げ（旧第5節→第4節）を確定し、目次を更新した。委員会資料は毎年度作成するものとする。委員会に諮ることが要件であるため、本文に結果を載せるだけでは要件を満たさない。手順を計画に位置づけ、資料を毎年度作ることで満たされる</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>介護給付適正化のケアプラン点検の着手（本文記載）</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月3日</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>(2)・(6)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月3日「確認事項2件はともにOKです。進めて下さい。」により①②を了承。ケアプラン点検実施要領（案）を作成した。③の点検件数は受託者案として、令和9年度264件（11事業所×4人×6か月分）、令和10年度396件、令和11年度528件を同要領の第7節に記載し、策定委員会でご協議いただく。④は同要領の第14節で確定を要する事項として引き続き管理する。主要3事業のうち1事業が未実施であることが外部データで裏づけられた。…</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>給付費データ集計　令和7年度の広域連合単位と3町合計の差</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月25日</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>(2)・(4)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度の給付費データの再提供を受けて点検した。従前のファイルの「介護度別給付費」の表は3,083,474,291円であったが、同じファイルの明細を集計すると3,213,054,558円となり、3町合計及び再提供を受けたファイルの表と要支援1から要介護5までの全7区分で円単位まで一致した。差は集計表が明細と一致していなかったことによるものであり、対象月、審査月又は住所地特例の扱いの違いによるものではない。…</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月15日</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>参照条文により、混合型特定施設入居者生活介護に係る必要利用定員総数は介護保険法第118条第4項により都道府県介護保険事業支援計画において定めることができる事項であり、第117条には現れないことを確かめた。介護専用型特定施設入居者生活介護に係る必要利用定員総数も第118条第2項第1号により都道府県が定める。すなわちいずれも本計画の記載事項ではない。当方が従前「第117条第3項の勘案事項」としていたのは誤りであった。…</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>年報（令和7年度）の様式別データのご提供</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月11日</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月11日に年報（令和7年度）の全様式を電子データで確認し、①〜④のすべてが得られた。②③④の要介護度別を確定値に置き換え、12で除した値が総括表詳細（１）と全24サービスで一致することを検算した（令和8年度実績見込み値の入力案 02〜06シート）。当該データは令和8年8月28日に受領済みの資料No.22と同一であり、当方が主要値のみを取り込み明細を取り込んでいなかったことによる起票であった。明細は確認のうえ収録した。…</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>実績見込み値の入力欄が小数を受け付けるか</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月11日</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月11日、弊社の別案件において実際に小数を入力して出力された推計結果により解決した。①利用者数（人数）の欄は整数で扱われる（同じ表で令和6・7年度の人数は小数10桁まで表示されるのに対し、編集した令和8年度の人数は全45サービスが整数、令和9〜11年度の推計値も全135件が整数）。②利用回（日）数の欄は小数第1位まで受け付ける。当方は人数を最大剰余法による整数版（要支援・要介護の群ごとの合計を保つ）、利用回（日）数を小数第1位版として用意した。…</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>155</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>全国自治体共通版の入力シート・手順書を本件に用いるか</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月18日</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>(5)・(7)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>全国自治体共通版の入力シート及び手順書はそのまま用いず、当方の試算によることとなった。記載の借用も行わない。これにより、同シートが担当者名及び連絡先を求める欄についての手当ては要しないこととなった。なお所得段階別13段階の推計（確認No.156）及び令和12・27・32年度の算定（確認No.157）は、見える化システム自体が求めるものであるため残り、いずれも当方で算定して解消した</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>同様の構成の団体との比較と団体名の扱い</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月29日</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>(2)・(6)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月29日に令和6・7・8年度の原本を受領し、3か年の比較を終えた。団体名の扱いについて同日ご指示をいただいた。協議用の資料には団体名を掲げてよく、計画素案には掲げない。掲げてよいこととなった場合は協議用の様式を計画に流用する。計画素案に他の団体の名が現れないことは成果品の自己点検で確かめている。なお他の保険者が策定した計画を参照して必要項目を導くことはご指示により行わない。代わりに評価指標の明細列と全国該当率による「全国の標準」から導いている</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月15日</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>(1)・(6)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>参照条文（001685804）の文字起こしのご提供を受け、介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した。改正されない項（第4項 作成の基準、第6項 加齢に伴う特性への留意、第7項 市町村老人福祉計画と一体、第10項 他計画との整合性の確保、第11項 他計画との調和、第12項 被保険者の意見の反映、第14項 都道府県知事への提出）の項番号が確定した。新旧対照条文と重なる6件の突合はいずれも一致した。…</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>注1　「何により決着したか」は回答・対応の欄の記述によります。長いものは句点で切っています。
+注2　決着の日付は回答・対応の欄に記された日付です。記載がないもの（No.49）は「―」としています。
+注3　決着したものはいずれも区分D（資料の徴求を要しないもの）です。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>資料提供依頼の台帳（23件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>資料のご提供をお願いしている事項は、確認事項の一覧とは別に資料提供依頼の台帳で管理しています。用途が異なるため1対1では対応しません。確認事項の一覧は素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用いています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>領域</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>確定する主張</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>入手先</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>希望時期</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>訪問・通所困難地域の判定</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>北海道・広域連合</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>3町</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>世帯構成の現状</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>総務省・3町</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>公表後</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>代替により解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>第9期の剰余額（現在は概算）</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>第7期（平成30〜令和2年度）の保険料条例</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>基準額が6,077円か5,900円かを確定する。</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>第7期の保険料基準額</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
+        <is>
+          <t>完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>第10期の段階設計と保険料算定</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>小学校区と日常生活圏域の対応関係</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>圏域別の分析、圏域設定の見直し</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>美瑛町・3町</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>第9期のプロセス評価（事業が計画どおり実施されたか）に必要。現時点で最大の空白。5区分14項目に展開し、記入様式を別冊「資料提供依頼_第9期の施策事業実績」（7シート）として作成した。既存資料（事務事業評価表、実施計画、介護保険事業状況報告、決算書）の写しのご提供でも足りる。</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>第9期の評価の完成</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="I17" s="18" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項35件の解消。</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>評価の枠組みの整理</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>地域差指数の分解の可否</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>給付費の地域内還流の議論</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>①区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。②区域内の地域密着型サービスは広域連合が指定権者であり、グループホームくるみの郷は介護サービス情報公表システムに掲載がないため定員を公表資料で確認できない。同事業所の定員及び休止の状況。③事業所票に所在町の記入欄がないため、事業所の所在町。</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H22" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>第2段階の算定チェーンは見える化B3・D45・D46系列により閉じた。残るのは、グループホーム・特定施設等の種別別受給者数と介護予防・日常生活支援総合事業の実績である。</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>サービス種別ごとの見込量の様式</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>第9期の令和6・7年度の確定値。見える化は年度途中で締めた値（令和6年度分は令和6年2月データ締め等）を収録しており、4月から3月までの通年の実績が確認できない。第3段階（給付費・保険料）の算定と、第9期の給付費の計画乖離（代表KPI H15）の把握に用いる。</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>第3段階の給付費の算定、H15の基準値</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I25" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告　月報（令和8年4月〜7月分）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度は年報が出ないため、月報により各月の進捗を確認する。令和8年度の実績は本業務の期間中に確定しないため、月報により推移を把握したうえで見える化ベースの試算により推定する。</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の推定、第9期の中間評価の更新</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I26" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>給付実績データ（サービス別の利用者数・利用日数等）（令和5年度〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の推定の基礎。月当たりの平均利用者数、利用者1人当たりの利用日数・回数。見える化のD系列では年度途中で締めた値となるサービスがあるため、保険者の給付実績により通年の値を確認する。</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>第2段階の見込量の精緻化、第3段階の給付費の算定</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>R8.8.31</t>
+        </is>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I27" s="18" t="inlineStr">
+        <is>
+          <t>解消</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>注1　受領又は解消したものは7件、なおご提供をお待ちしているものは16件です。
+注2　備考に記した確認事項の番号は、起票した時点のものです。
+注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -996,7 +3889,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>自己点検（22件）</t>
+          <t>自己点検（32件）</t>
         </is>
       </c>
     </row>
@@ -1053,7 +3946,7 @@
           <t>台帳189件・分類189件・分類にないNo. なし</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1078,7 +3971,7 @@
           <t>台帳にないNo. なし</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1103,7 +3996,7 @@
           <t>63＋7＋3＋96＋20＝189（台帳189）</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1128,7 +4021,7 @@
           <t>定めのない記号を持つNo. なし</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1153,7 +4046,7 @@
           <t>定めのない記号を持つNo. なし</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1178,7 +4071,7 @@
           <t>欠けているNo. なし</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1203,7 +4096,7 @@
           <t>欠けているNo. なし</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1228,7 +4121,7 @@
           <t>未決173件・既定値のないNo. なし</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1253,7 +4146,7 @@
           <t>区分の付かないNo. なし</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1278,7 +4171,7 @@
           <t>決着済み16件・区分Dに入っていないNo. なし</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1303,7 +4196,7 @@
           <t>優先5件・区分Aにない No. なし</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1328,7 +4221,7 @@
           <t>7件（[33, 93, 105, 106, 110, 112, 137]）</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1353,7 +4246,7 @@
           <t>63件／区分A 63件・当たらないNo. なし</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1378,7 +4271,7 @@
           <t>23件（受領又は解消7件）</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1403,7 +4296,7 @@
           <t>当たり0件</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1428,7 +4321,7 @@
           <t>当たり0件</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1453,7 +4346,7 @@
           <t>当たり0件</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1478,7 +4371,7 @@
           <t>当たり0件</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1503,7 +4396,7 @@
           <t>当たり0種</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1528,7 +4421,7 @@
           <t>当たり0件</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1553,7 +4446,7 @@
           <t>57＋6＝63（区分A 63）</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1578,16 +4471,266 @@
           <t>7件（[68, 123, 124, 125, 132, 136, 138]）</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>判定　適合22件・不適合0件</t>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>不足している情報の性質が区分Aの全件を覆うこと</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>区分AのNo.の集合 − 性質に当たったNo.の集合</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>区分A 63件・覆った63件・当たらないもの なし</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>性質のいずれの区分も0件でないこと</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>性質ごとの件数を数える</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ア 33件／イ 17件／ウ 12件／エ 23件／オ 18件／カ 9件／キ 10件</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>確認事項の業務内容の記号が仕様書の記号に当たること</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>台帳の記号の集合 − 業務工程管理表の業務内容の記号の集合</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>台帳11種・仕様書12種・仕様書にない記号 なし</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>業務内容の記号が付されていない確認事項がないこと</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>台帳の業務内容の欄から「(数字)」を拾う</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>記号のないもの なし</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>動かせない日程が業務工程管理表の月別工程に現にあること</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>月別工程の成果物・状況の欄を走査する</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>6件のうち現にないもの なし</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>日程ごとの件数が未決の部分集合であり0件でないこと</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>日程ごとの数え方で未決を絞る</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月30日 85件／令和8年11月13日 85件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 173件／令和9年3月23日 173件</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="13" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>決着しないと当方の作業が止まるものがないこと</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>未決のうち決着しない場合の扱いがないものと、据え置きの区分Aを数える</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>扱いのないもの0件・据え置きの区分A 0件</t>
+        </is>
+      </c>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>決着した事項が全件区分Dであること</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>決着したNo.のうち区分Dでないものを数える</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>決着16件・区分Dでないもの なし</t>
+        </is>
+      </c>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>決着した事項の全件に何により決着したかが書かれていること</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>回答・対応の欄から経緯を切り出し、10文字未満のものを数える</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>経緯の短いもの なし</t>
+        </is>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>決着と未決の和が台帳の件数と一致すること</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>決着の件数 ＋ 未決の件数 ＝ 台帳の件数</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>16＋173＝189（台帳 189）</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>判定　適合32件・不適合0件</t>
         </is>
       </c>
     </row>
@@ -1595,7 +4738,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A37:E37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1607,7 +4750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1630,7 +4773,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>区分ごとの件数と、その内訳（出どころ別・状態別・保険料の月額への効き）です。区分の判定は確認事項ごとに行っており、02シート から 06シート に明細があります。</t>
+          <t>区分ごとの件数と、その内訳（出どころ別・状態別・保険料の月額への効き）です。区分の判定は確認事項ごとに行っており、03シート から 07シート に明細があります。</t>
         </is>
       </c>
     </row>
@@ -2234,24 +5377,212 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>5　不足している情報の性質（区分A）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>性質</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>ア　事業の実施状況・実績の記録</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>33</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>3町及び広域連合が事業として行った量・費用の記録。国の調査の様式では区分が足りず、当方では作れない</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="12" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>イ　供給側の実態</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>事業所の定員・稼働・休廃止・類型。見込量の上限と必要利用定員総数に直結する</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="12" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>ウ　制度・運用の定め</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>広域連合の条例・規約、算定の運用。法定記載事項の根拠となる</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="12" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>エ　当方が接続できない画面・公表資料</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>公表されているか、保険者であれば画面から得られるもの。当方の作業環境は外部の情報提供サイトへ接続できない</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="12" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>オ　調査・集計の条件</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>既に受領している数値の母数・分母・抽出の条件。値そのものではなく、値の読み方が確定しない</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="12" t="n"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="6" t="inlineStr"/>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>カ　他の計画・関係機関の状況</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>3町の計画、北海道の方針、関係機関の取組。計画の調和と連携の記述に用いる</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="12" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>キ　既に受領している統計の年次・区分の不足</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>統計そのものは受領しているが、年次又は区分が足りないもの。一次統計は不足していない。</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="12" t="n"/>
+    </row>
+    <row r="45" ht="104" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（122件）は区分Aの63件を上回ります。
+注2　不足しているのは一次統計ではありません。介護保険事業状況報告（年報・月報）、国勢調査、住民基本台帳、見える化システムの指標、交付金の全国集計、総合事業の実施状況に関する調査はいずれも受領しており、サービス見込量・給付費・保険料の算定はこれらにより行っています。不足しているのは、①3町及び広域連合が事業として行った量・費用の記録、②事業所の定員・稼働の実態、③広域連合の条例・規約及び算定の運用、④既に受領している統計の年次又は区分です。
+注3　性質の判定は件名・確認をお願いする内容・徴求する資料の記述によります。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="28">
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="F18:H18"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="D40:H40"/>
     <mergeCell ref="D27:H27"/>
+    <mergeCell ref="D41:H41"/>
     <mergeCell ref="D32:H32"/>
+    <mergeCell ref="D43:H43"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="F16:H16"/>
+    <mergeCell ref="D39:H39"/>
     <mergeCell ref="D25:H25"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D42:H42"/>
     <mergeCell ref="D33:H33"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="D38:H38"/>
     <mergeCell ref="F15:H15"/>
     <mergeCell ref="D26:H26"/>
     <mergeCell ref="A34:H34"/>
@@ -2261,6 +5592,770 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>仕様書の業務内容別の確認事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>確認事項を、仕様書が定める業務内容ごとに数えたものです。どの業務にご確認・ご判断が集まっているかを示します。一つの確認事項が複数の業務内容にわたるため、それぞれの行に数えています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1　業務内容ごとの件数と区分の内訳</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>記号</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>業務内容（仕様書）</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>確認事項</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>うち未決</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>区分A</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>区分B・B待</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>区分C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>区分D</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>月額に効く</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>法第117条に関わる</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>進捗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>制度改正等の整理</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>83％</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の評価・検証</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>93％</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>実施済み調査結果の集計・分析</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>79％</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>現状分析及び地域課題の整理</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>94％</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>将来推計</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>81％</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>計画書の作成</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>50％</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>計画策定支援</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>62％</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>各種会議への技術的支援</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>50％</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>(9)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>パブリックコメント支援</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>12％</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>成果品の作成</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>62％</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="104" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の189件を上回ります。
+注2　進捗は作業項目の達成状況による算定です。(11)成果品の帰属及び(12)その他は進捗の対象ではないため「―」です。
+注3　業務内容の記号が付されていない確認事項はありません。確認事項のない業務内容（(11) 成果品の帰属）は掲げていません。
+注4　確認事項が最も多い業務内容は(6) 計画書の作成、進捗が最も低い業務内容は(9) パブリックコメント支援です。ご判断・ご決定を求めるものが49件あり、計画への記載の仕方の決定がここに集まっています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2　確認事項が最も集まっている業務内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>記号</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>業務内容（仕様書）</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>確認事項</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>うち未決</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>そのうち資料の徴求を要するもの</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>そのうちご判断・ご決定を求めるもの</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>計画書の作成</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>20件（66・73・74・81・90・91・92・93・95・96・99・112）</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>49件</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="12" t="n"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>将来推計</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>25件（15・16・30・36・47・50・52・68・78・82・93・102）</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>36件</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="12" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画の評価・検証</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>14件（5・6・7・23・34・48・56・58・73・74・90・91）</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>14件</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="12" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>現状分析及び地域課題の整理</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>9件（11・12・13・26・66・76・77・81・184）</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>6件</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="12" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>注1　上位4つの業務内容を掲げました。確認事項のNo.は13件目以降を省いています。全件は03シート（資料の徴求を要するもの）及び06シート（ご判断・ご決定を求めるもの）に掲げています。
+注2　同じ確認事項が複数の業務内容に現れるため、上位4つの件数の和は確認事項の総数と一致しません。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="F24:K24"/>
+    <mergeCell ref="F23:K23"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="F22:K22"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="F21:K21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2290,7 +6385,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>広域連合、構成3町、北海道、国民健康保険団体連合会その他、広域連合を通じてでなければ得られない記録によるものです。公表されていないため当方では確認できません。資料が届かない場合の扱いは 03シート にあります。</t>
+          <t>広域連合、構成3町、北海道、国民健康保険団体連合会その他、広域連合を通じてでなければ得られない記録によるものです。公表されていないため当方では確認できません。資料が届かない場合の扱いは 04シート にあります。</t>
         </is>
       </c>
     </row>
@@ -5196,7 +9291,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5292,7 +9387,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5327,7 +9422,7 @@
           <t>公表資料・年報・総括表</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5362,7 +9457,7 @@
           <t>公表資料</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5397,7 +9492,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5432,7 +9527,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5467,7 +9562,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5502,7 +9597,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5537,7 +9632,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5572,7 +9667,7 @@
           <t>北海道の名簿・指定事業所一覧</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5607,7 +9702,7 @@
           <t>年報・総括表</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5642,7 +9737,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5677,7 +9772,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5712,7 +9807,7 @@
           <t>公表資料・北海道の名簿・指定事業所一覧</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5747,7 +9842,7 @@
           <t>3町の実施報告書・受領済みの資料</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5782,7 +9877,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5817,7 +9912,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5852,7 +9947,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5887,7 +9982,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5922,7 +10017,7 @@
           <t>年報・総括表</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F23" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5957,7 +10052,7 @@
           <t>受領済みの資料</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -5992,7 +10087,7 @@
           <t>年報・総括表・受領済みの資料</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F25" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6027,7 +10122,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6062,7 +10157,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F27" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6097,7 +10192,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F28" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6132,7 +10227,7 @@
           <t>北海道の名簿・指定事業所一覧</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F29" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6167,7 +10262,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F30" s="17" t="inlineStr">
+      <c r="F30" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6202,7 +10297,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F31" s="17" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6237,7 +10332,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F32" s="17" t="inlineStr">
+      <c r="F32" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6272,7 +10367,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F33" s="17" t="inlineStr">
+      <c r="F33" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6307,7 +10402,7 @@
           <t>公表資料</t>
         </is>
       </c>
-      <c r="F34" s="17" t="inlineStr">
+      <c r="F34" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6342,7 +10437,7 @@
           <t>北海道の名簿・指定事業所一覧</t>
         </is>
       </c>
-      <c r="F35" s="17" t="inlineStr">
+      <c r="F35" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6377,7 +10472,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F36" s="17" t="inlineStr">
+      <c r="F36" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6412,7 +10507,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F37" s="17" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6447,7 +10542,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F38" s="17" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6482,7 +10577,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F39" s="17" t="inlineStr">
+      <c r="F39" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6517,7 +10612,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="F40" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6552,7 +10647,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F41" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6587,7 +10682,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F42" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6622,7 +10717,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -6657,7 +10752,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F44" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6692,7 +10787,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F45" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6727,7 +10822,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F46" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6762,7 +10857,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F47" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6797,7 +10892,7 @@
           <t>3町の実施報告書</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F48" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6832,7 +10927,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F49" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6867,7 +10962,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F50" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6902,7 +10997,7 @@
           <t>年報・総括表</t>
         </is>
       </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6937,7 +11032,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -6972,7 +11067,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F53" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7007,7 +11102,7 @@
           <t>年報・総括表</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F54" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7042,7 +11137,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="F55" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7077,7 +11172,7 @@
           <t>受領済みの資料</t>
         </is>
       </c>
-      <c r="F56" s="17" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7112,7 +11207,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F57" s="17" t="inlineStr">
+      <c r="F57" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7147,7 +11242,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F58" s="17" t="inlineStr">
+      <c r="F58" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7182,7 +11277,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F59" s="17" t="inlineStr">
+      <c r="F59" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7217,7 +11312,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F60" s="17" t="inlineStr">
+      <c r="F60" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7252,7 +11347,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F61" s="18" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -7287,7 +11382,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F62" s="17" t="inlineStr">
+      <c r="F62" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7322,7 +11417,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F63" s="18" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -7357,7 +11452,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F64" s="18" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -7392,7 +11487,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F65" s="18" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -7427,7 +11522,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F66" s="17" t="inlineStr">
+      <c r="F66" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -7462,7 +11557,7 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F67" s="18" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -7493,7 +11588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8155,7 +12250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12560,7 +16655,7 @@
     <row r="101" ht="70" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>注1　ご判断をいただかなくても算定は止まりません。全件に決着しない場合の扱い（既定値）を置いているためです。既定値は 03シート 及び業務工程管理表 03 確認事項一覧の回答欄に掲げています。
+          <t>注1　ご判断をいただかなくても算定は止まりません。全件に決着しない場合の扱い（既定値）を置いているためです。既定値は 04シート 及び業務工程管理表 03 確認事項一覧の回答欄に掲げています。
 注2　既定値は協議を進めるための仮置きであり、公表の確定の根拠にはなりません。
 注3　「併せて要するもの」がある21件は、ご判断の前提として資料又は事実の確認を要します。</t>
         </is>
@@ -12576,7 +16671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12677,7 +16772,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G5" s="17" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
@@ -12712,7 +16807,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -12747,7 +16842,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -12782,7 +16877,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
@@ -12852,7 +16947,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>了承済（保管せず廃棄）</t>
         </is>
@@ -12922,7 +17017,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
@@ -12957,7 +17052,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -12992,7 +17087,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
@@ -13027,7 +17122,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
@@ -13062,7 +17157,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
@@ -13097,7 +17192,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G17" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
@@ -13132,7 +17227,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -13167,7 +17262,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G19" s="18" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -13202,7 +17297,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>了承済</t>
         </is>
@@ -13307,7 +17402,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G23" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
@@ -13342,7 +17437,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
@@ -13366,7 +17461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13927,7 +18022,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -13962,7 +18057,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G25" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -13997,7 +18092,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -14032,7 +18127,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -14067,7 +18162,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G28" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -14102,7 +18197,7 @@
           <t>②　未確定箇所として残す</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="G29" s="19" t="inlineStr">
         <is>
           <t>未確定箇所が残る</t>
         </is>
@@ -14137,7 +18232,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G30" s="17" t="inlineStr">
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14172,7 +18267,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G31" s="17" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14207,7 +18302,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14242,7 +18337,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G33" s="17" t="inlineStr">
+      <c r="G33" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14277,7 +18372,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G34" s="17" t="inlineStr">
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14312,7 +18407,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G35" s="17" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14347,7 +18442,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G36" s="17" t="inlineStr">
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14382,7 +18477,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14417,7 +18512,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14452,7 +18547,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G39" s="17" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14487,7 +18582,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G40" s="17" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14522,7 +18617,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14557,7 +18652,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14592,7 +18687,7 @@
           <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
-      <c r="G43" s="17" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>確定できる</t>
         </is>
@@ -14767,1140 +18862,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>資料提供依頼の台帳（23件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="58" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>資料のご提供をお願いしている事項は、確認事項の一覧とは別に資料提供依頼の台帳で管理しています。用途が異なるため1対1では対応しません。確認事項の一覧は素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用いています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>領域</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>資料</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>確定する主張</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>入手先</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>希望時期</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>優先度</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>調整済み認定率は令和7年3月末までしか出力されていない。第9期の評価には令和8年3月末（令和7年度末）の値が必要。</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>中重度・軽度の認定率の推移</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>見える化システム</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>訪問系・通所系事業所の運営規程における通常の事業の実施地域【令和8年8月4日受領済】</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>居宅サービスは北海道、地域密着型は広域連合が保有する。訪問・通所困難地域の判定の唯一の客観的根拠。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に収録されており、区域内124件を抽出して整理した。</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>訪問・通所困難地域の判定</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>北海道・広域連合</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかを検証する。</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>高齢者単身世帯・夫婦世帯の最新値。公表され次第。</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>代替により解消</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>自給率（δ）は見える化から受領し、区域外の事業所による給付の割合が確定した（R8.7.30）。残るのは区域外事業所の所在地の特定（No.18）と町別給付費による金額換算（No.17）である。</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>発注者・国保連</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数（令和4〜8年度）、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少（234人→160人）の経緯。</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者における組合せ。</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H12" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>第7期から第9期の各年度。令和8年度末の残高見込を含む。</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>第9期の剰余額（現在は概算）</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>第7期（平成30〜令和2年度）の保険料条例</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>基準額が6,077円か5,900円かを確定する。</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>第7期の保険料基準額</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>標準段階数、標準乗率、公費軽減の乗率、第1号被保険者負担割合。</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>第10期の段階設計と保険料算定</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>国の情報</t>
-        </is>
-      </c>
-      <c r="G15" s="13" t="inlineStr">
-        <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明。</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町・3町</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>第9期のプロセス評価（事業が計画どおり実施されたか）に必要。現時点で最大の空白。5区分14項目に展開し、記入様式を別冊「資料提供依頼_第9期の施策事業実績」（7シート）として作成した。既存資料（事務事業評価表、実施計画、介護保険事業状況報告、決算書）の写しのご提供でも足りる。</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>令和8年8月4日に102ファイルを受領。残るのは点検事項35件の解消。</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="40" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>介護保険法第117条に基づく評価・公表の実績。受託者の評価との対照に必要。</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>評価の枠組みの整理</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムD49の指標定義</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>性・年齢調整の適用範囲と指数化の基準。受給率×受給者単価が給付月額指数に一致しない理由の特定に必要。</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>地域差指数の分解の可否</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>見える化システム・厚生労働省</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の加重平均の算定にも必要。</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>給付費の地域内還流の議論</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>発注者・国保連</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>①区域外の事業所が旭川市か他の市町村かを特定する。圏域を越えた利用の調整（第6章第4節）の根拠となる。②区域内の地域密着型サービスは広域連合が指定権者であり、グループホームくるみの郷は介護サービス情報公表システムに掲載がないため定員を公表資料で確認できない。同事業所の定員及び休止の状況。③事業所票に所在町の記入欄がないため、事業所の所在町。</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>発注者・国保連</t>
-        </is>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>第2段階の算定チェーンは見える化B3・D45・D46系列により閉じた。残るのは、グループホーム・特定施設等の種別別受給者数と介護予防・日常生活支援総合事業の実績である。</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>サービス種別ごとの見込量の様式</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>分析資料に付した留保（確認していない範囲、概算値である旨、単純平均か加重平均か、時点の違い等）が、会議資料へ転記する際に落ちていないかを照合する。キックオフ資料の自己点検で、12件中5件がこの類であった。</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>受託者</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>第9期の令和6・7年度の確定値。見える化は年度途中で締めた値（令和6年度分は令和6年2月データ締め等）を収録しており、4月から3月までの通年の実績が確認できない。第3段階（給付費・保険料）の算定と、第9期の給付費の計画乖離（代表KPI H15）の把握に用いる。</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>第3段階の給付費の算定、H15の基準値</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業状況報告　月報（令和8年4月〜7月分）</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度は年報が出ないため、月報により各月の進捗を確認する。令和8年度の実績は本業務の期間中に確定しないため、月報により推移を把握したうえで見える化ベースの試算により推定する。</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の推定、第9期の中間評価の更新</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>受領済</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>給付実績データ（サービス別の利用者数・利用日数等）（令和5年度〜令和7年度）</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量の推定の基礎。月当たりの平均利用者数、利用者1人当たりの利用日数・回数。見える化のD系列では年度途中で締めた値となるサービスがあるため、保険者の給付実績により通年の値を確認する。</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>第2段階の見込量の精緻化、第3段階の給付費の算定</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>R8.8.31</t>
-        </is>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>解消</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>注1　受領又は解消したものは7件、なおご提供をお待ちしているものは16件です。
-注2　備考に記した確認事項の番号は、起票した時点のものです。
-注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A2:I2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -1201,7 +1201,7 @@
           <t>注1　確認事項は189件（うちご決定・ご確認をお待ちしているもの173件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は受託者が仮に置くものであり、決定ではありません。令和8年10月の意見交換会で内容をお諮りします。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月15日</t>
+注4　基準日　令和8年10月16日</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した。【令和8年10月15日】参照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって地域密着型特定施設でないもの」であることを2つ目の原典で確かめた。また同条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まることが分かった</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -1198,10 +1198,10 @@
     <row r="43" ht="86" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項は189件（うちご決定・ご確認をお待ちしているもの173件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
-注2　「資料が届かない場合の扱い」は受託者が仮に置くものであり、決定ではありません。令和8年10月の意見交換会で内容をお諮りします。
+          <t>注1　確認事項は189件（うち受託者案で確定したもの173件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
+注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月16日</t>
+注4　基準日　令和8年10月19日</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>優先（6点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>優先（8点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -1916,106 +1916,106 @@
     </row>
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>150</v>
+        <v>7</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>優先（7点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
+          <t>④　現に確認できている値で確定する</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>④　現に確認できている値で確定する</t>
+          <t>②　未確定箇所として残す</t>
         </is>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>②　未確定箇所として残す</t>
+          <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>93％</t>
+          <t>96％</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>79％</t>
+          <t>100％</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>94％</t>
+          <t>100％</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>81％</t>
+          <t>88％</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>50％</t>
+          <t>80％</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>62％</t>
+          <t>75％</t>
         </is>
       </c>
     </row>
@@ -6439,26 +6439,26 @@
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>112</v>
+        <v>2</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -6468,52 +6468,52 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>最大7円</t>
+          <t>受託者案で確定（告示後に再算定）</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>優先（8点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
+          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -6523,52 +6523,52 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>優先（7点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
+          <t>素案 第3章第4節 追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>最大47円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>優先（6点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -6613,17 +6613,17 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
+          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
+          <t>素案 第2章第4〜6節 クロス集計表</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -6658,17 +6658,17 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6678,22 +6678,22 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
+          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>素案 第4章第3節 H14の基準値</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -6703,42 +6703,42 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・総務省</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
+          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
+          <t>素案 第2章第1節 図1・図2・図3</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -6748,42 +6748,42 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
+          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
@@ -6793,42 +6793,42 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援2事業所ほかの指定の状況</t>
+          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
+          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
@@ -6838,42 +6838,42 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>68</v>
+        <v>15</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
+          <t>令和3年度から令和8年度までの各月の認定者数</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -6883,42 +6883,42 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
+          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
+          <t>素案 第6章第3節・第6節 保険料算定表</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
+          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -6973,32 +6973,32 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
+          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
+          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -7018,42 +7018,42 @@
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>3町・北海道</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
+          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
+          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H18" s="13" t="inlineStr">
@@ -7063,32 +7063,32 @@
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>広域連合・国民健康保険団体連合会</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
+          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
+          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H19" s="13" t="inlineStr">
@@ -7108,17 +7108,17 @@
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -7128,22 +7128,22 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
+          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
+          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H20" s="13" t="inlineStr">
@@ -7153,42 +7153,42 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
+          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -7198,17 +7198,17 @@
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -7218,22 +7218,22 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
+          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
+          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -7243,42 +7243,42 @@
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
+          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
+          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -7288,32 +7288,32 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
+          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
+          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -7333,17 +7333,17 @@
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
+          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節 追加調査報告書 02シート</t>
+          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -7378,17 +7378,17 @@
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7398,22 +7398,22 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
+          <t>一般介護予防事業費がどの科目で執行されているか</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節 クロス集計表</t>
+          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -7423,17 +7423,17 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
+          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節 H14の基準値</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -7468,42 +7468,42 @@
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>3町・総務省</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節 図1・図2・図3</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -7513,42 +7513,42 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
+          <t>居宅介護支援2事業所ほかの指定の状況</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
+          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -7558,42 +7558,42 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
+          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節 保険料算定表</t>
+          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -7603,32 +7603,32 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
+          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
+          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -7648,42 +7648,42 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
+          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
+          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -7693,42 +7693,42 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
+          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
+          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -7738,42 +7738,42 @@
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
+          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
+          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -7783,42 +7783,42 @@
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費がどの科目で執行されているか</t>
+          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
+          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -7828,42 +7828,42 @@
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
+          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -7998,7 +7998,7 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -8053,32 +8053,32 @@
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
+          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
+          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -8088,42 +8088,42 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>最大47円</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
+          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
+          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -8143,32 +8143,32 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>121</v>
+        <v>96</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -8188,32 +8188,32 @@
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
+          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
+          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -8233,32 +8233,32 @@
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
+          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -8278,32 +8278,32 @@
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
+          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -8323,32 +8323,32 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -8358,42 +8358,42 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>最大7円</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
+          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -8413,17 +8413,17 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -8458,32 +8458,32 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・項目定義</t>
+          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 将来推計 第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -8503,42 +8503,42 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座の開催回数・修了者数</t>
+          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -8548,42 +8548,42 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -8593,42 +8593,42 @@
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>東神楽町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
+          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H53" s="13" t="inlineStr">
@@ -8638,32 +8638,32 @@
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>2</v>
+        <v>136</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
+          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H54" s="13" t="inlineStr">
@@ -8683,32 +8683,32 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -8728,17 +8728,17 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>15</v>
+        <v>148</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -8748,22 +8748,22 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>令和3年度から令和8年度までの各月の認定者数</t>
+          <t>見える化システムの操作手引・項目定義</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>見える化システムへの入力 将来推計 第2段階</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -8773,42 +8773,42 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H57" s="13" t="inlineStr">
@@ -8818,42 +8818,42 @@
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>23</v>
+        <v>160</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
+          <t>認知症サポーター養成講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -8863,32 +8863,32 @@
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>3町・北海道</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
+          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -8908,42 +8908,42 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
+          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8988,7 @@
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9033,7 +9033,7 @@
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -9133,7 +9133,7 @@
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -9223,7 +9223,7 @@
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>一部提供（R8.10.14）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -12218,7 +12218,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -12334,26 +12334,26 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針（4件）</t>
+          <t>類似保険者の選定条件と比較対象の保険者</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東川町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第2章第2節・第6章第2節・第4節 構成町の意見への回答 6</t>
+          <t>素案 第2章第2節 分析資料</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -12373,42 +12373,42 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数の基盤整備単位、認知症対応型共同生活介護の圏域別の定員</t>
+          <t>代表KPI H07・H08・H12・H16を代理指標へ振り替えるかどうか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第7節・第6章第4節4 サービス見込量の算定</t>
+          <t>素案 第4章第3節・資料1 全16KPIの4項目</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -12418,42 +12418,42 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>3調査の点検事項（重大6件）の取扱いと、事業所への照会の要否</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
+          <t>素案 第2章第5・6節 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -12463,22 +12463,22 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びにサービス別の趨勢を半分反映するか</t>
+          <t>人口推計の基礎とする系列（社人研推計か3町の総合計画か）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -12488,42 +12488,42 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>最大58円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>3町の第10期計画へ共通指標を掲載することの合意</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -12533,17 +12533,17 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
+          <t>素案 資料2 3町協議資料</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H9" s="13" t="inlineStr">
@@ -12553,22 +12553,22 @@
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>中長期推計をどこまで算定し、どこまで計画本文に掲げるか</t>
+          <t>骨子案（章立て・基本理念・基本目標・代表KPIの枠組み）</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -12578,17 +12578,17 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第2章第8節・第6章第2節</t>
+          <t>骨子案 素案の次稿</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H10" s="13" t="inlineStr">
@@ -12598,42 +12598,42 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>策定委員会の開催日程・審議事項・資料提出期限、意見公募手続の期間、町別値の公表基準</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第2節・第4節</t>
+          <t>委員会資料原案 パブリックコメント資料</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H11" s="13" t="inlineStr">
@@ -12643,22 +12643,22 @@
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画の扱い</t>
+          <t>成果品の仕様（章別の頁配分・図表の掲載点数・概要版・入稿期限）</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -12668,17 +12668,17 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2</t>
+          <t>計画書（印刷200部） 概要版</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H12" s="13" t="inlineStr">
@@ -12688,32 +12688,32 @@
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>北海道の評価指標のうち「市町村数」を単位とするものの読替えの考え方</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（北海道）</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節・第3節 サービス見込量の算定</t>
+          <t>素案 第1章第6節 追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H13" s="13" t="inlineStr">
@@ -12733,22 +12733,22 @@
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>152</v>
+        <v>24</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>24時間対応サービスの確保方策（4案のいずれか）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -12758,17 +12758,17 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第6章第2節・第4節 見込量表（3種別）</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H14" s="13" t="inlineStr">
@@ -12778,22 +12778,22 @@
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cから変化率法に改めるか</t>
+          <t>代表KPIの令和11年度目標値</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -12803,17 +12803,17 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第4章第3節・第5章 全16KPIの目標値</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H15" s="13" t="inlineStr">
@@ -12823,22 +12823,22 @@
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>通常（5点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>86</v>
+        <v>28</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>交付金の交付見込額を保険料収納必要額から控除するか</t>
+          <t>各調査の対象者の範囲（母集団が異なる指標を併記する前提）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第6節 将来推計 第3段階 保険料算定式の国の様式との対照</t>
+          <t>調査クロス集計・分析 13・14シート H06・H11の基準値</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H16" s="13" t="inlineStr">
@@ -12868,22 +12868,22 @@
       </c>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案B）の反映内容</t>
+          <t>重度化の速度の前提（3案のいずれか）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -12893,17 +12893,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標5・資料5 給付適正化計画の位置づけと追加検討事項</t>
+          <t>素案 第6章第1節 認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H17" s="13" t="inlineStr">
@@ -12913,22 +12913,22 @@
       </c>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>給付適正化を第10期に実施するか、推計へ政策効果として見込むか</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -12938,42 +12938,42 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第4章第3節・第6章第2節</t>
+          <t>素案 第6章第2節・第5章・第7章 給付費の推計</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>最大13円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないこと</t>
+          <t>中間報告・施策体系新旧対照表・骨子案の内容</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -12983,87 +12983,87 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第5章 基本目標5・第6章第2節</t>
+          <t>計画骨子案 施策体系新旧対照表 計画素案 第4章・第5章</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>最大327円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>社会資源一覧の従業員数を延べとするか施設単位の実人数とするか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>従業員数の重複計上の整理 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>最大327円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>通常（4点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案の内容</t>
+          <t>認定に要する日数を第9期の評価・第10期の課題として扱うか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>計画骨子案 施策体系新旧対照表 計画素案 第4章・第5章</t>
+          <t>中間報告 第3節 計画素案 第2章・第5章</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H21" s="13" t="inlineStr">
@@ -13093,32 +13093,32 @@
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数を延べとするか施設単位の実人数とするか</t>
+          <t>代表KPI H15の分母（標準給付費見込額か総給付費か）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>従業員数の重複計上の整理 計画素案 第2章第3節・第6章第2節</t>
+          <t>計画素案 第4章 資料1 中間報告 第3節</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H22" s="13" t="inlineStr">
@@ -13138,22 +13138,22 @@
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数を第9期の評価・第10期の課題として扱うか</t>
+          <t>月報の値の接続のずれ3件の確認</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>中間報告 第3節 計画素案 第2章・第5章</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H23" s="13" t="inlineStr">
@@ -13183,32 +13183,32 @@
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母（標準給付費見込額か総給付費か）</t>
+          <t>基金の積立ての上限の解釈と第10期の取崩方針</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章 資料1 中間報告 第3節</t>
+          <t>基金条例の確認 02シート 素案 第6章第6節 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H24" s="13" t="inlineStr">
@@ -13228,22 +13228,22 @@
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービス2件の第10期の計画値の置き方</t>
+          <t>議事録の文書プロパティから個人情報を削除する運用</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>中間報告会議議事録 業務工程管理表</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -13263,7 +13263,7 @@
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H25" s="13" t="inlineStr">
@@ -13273,22 +13273,22 @@
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とすること（案C）</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎の変更_総合戦略ベース 将来推計 第1〜3段階 計画素案 第2章第1節・第6章</t>
+          <t>中間報告会議議事録 業務工程管理表</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H26" s="13" t="inlineStr">
@@ -13318,22 +13318,22 @@
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>計画値を0としたサービス2件の第10期の計画値の置き方</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位 介護高齢者福祉サービスガイド_構成案 計画素案 第5章・第6章第3節2</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H27" s="13" t="inlineStr">
@@ -13363,22 +13363,22 @@
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果2件）</t>
+          <t>調整交付金の算定基礎に包括的支援事業費・任意事業費を含めない扱い</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>算定方法の整合確認（国と見える化） 将来推計 第2段階・第3段階 計画素案 第6章第3節・第6節</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H28" s="13" t="inlineStr">
@@ -13408,22 +13408,22 @@
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位を計画本文に掲げるか</t>
+          <t>第10期の保険料算定の前提4件</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -13433,17 +13433,17 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第4節 図表集 27シート 交付金評価指標と全国集計の受領点検 04シート</t>
+          <t>将来推計 第3段階 05・06シート 計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -13453,22 +13453,22 @@
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと「第10期へ引き継ぐ改善事項」の再整理案</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -13478,17 +13478,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章・資料1 骨子案 第4節 図表集31シート 代表KPIの振替案と確認事項の精査</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -13498,22 +13498,22 @@
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策の数にも簡素化の考え方を及ぼすか</t>
+          <t>人口推計の基礎を地方創生総合戦略とすること（案C）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -13523,17 +13523,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 骨子案 第5節</t>
+          <t>人口推計の基礎の変更_総合戦略ベース 将来推計 第1〜3段階 計画素案 第2章第1節・第6章</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H31" s="13" t="inlineStr">
@@ -13543,22 +13543,22 @@
       </c>
       <c r="I31" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型5件を計画に掲げるか</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節1 計画素案 第6章第2節2（2） サービス見込量の算定</t>
+          <t>介護高齢者福祉サービスガイド_構成案 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
@@ -13588,22 +13588,22 @@
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -13613,17 +13613,17 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節・第3節・第6節</t>
+          <t>広域連合において行うべき事業の優先順位 介護高齢者福祉サービスガイド_構成案 計画素案 第5章・第6章第3節2</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H33" s="13" t="inlineStr">
@@ -13633,22 +13633,22 @@
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の見込量の表の数値の差し替え</t>
+          <t>算定方法の国の様式との整合（点検結果2件）</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -13658,17 +13658,17 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2 サービス見込量の算定</t>
+          <t>算定方法の整合確認（国と見える化） 将来推計 第2段階・第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
@@ -13678,32 +13678,32 @@
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>成果指向型配分枠への対応、3町の該当状況調査の回答</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（3町）</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
+          <t>計画素案 第5章 交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H35" s="13" t="inlineStr">
@@ -13723,32 +13723,32 @@
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>施設及び居住系の実績の減少を将来へ延長するか</t>
+          <t>交付金の全国順位を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第4節4</t>
+          <t>計画素案 第3章第4節 図表集 27シート 交付金評価指標と全国集計の受領点検 04シート</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H36" s="13" t="inlineStr">
@@ -13768,32 +13768,32 @@
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される3区分を見込量に立てるか</t>
+          <t>代表KPIと「第10期へ引き継ぐ改善事項」の再整理案</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>公表を待つもの（国の政令・省令）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第1章第9節・第6章第2節・第4節</t>
+          <t>計画素案 第4章第3節・第5章・資料1 骨子案 第4節 図表集31シート 代表KPIの振替案と確認事項の精査</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -13813,22 +13813,22 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料（転載を禁ずる記載のある2件）の取扱い</t>
+          <t>第5章の施策の数にも簡素化の考え方を及ぼすか</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の受領点検とKPI設計案 計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 骨子案 第5節</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H38" s="13" t="inlineStr">
@@ -13858,22 +13858,22 @@
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>職員個票のリストによる重複の確認を行うか</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第4節・第4章第3節</t>
+          <t>内部確認結果への対応整理 03・08 実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -13903,32 +13903,32 @@
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い、区域外利用の把握の手段</t>
+          <t>構成町との意見交換会の実施方法</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節4 サービス見込量の算定</t>
+          <t>意見交換会資料 町別データシート 構成町の意見への回答 2・3</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
@@ -13948,32 +13948,32 @@
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>146</v>
+        <v>84</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>東川町の施設整備・サービス提供方針（4件）</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東川町）</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+          <t>サービス見込量 第2次概算 計画素案 第2章第2節・第6章第2節・第4節 構成町の意見への回答 6</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
@@ -13993,22 +13993,22 @@
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>151</v>
+        <v>85</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外すか</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+          <t>町別データシート 構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
@@ -14038,22 +14038,22 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>通常（3点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>類似保険者の選定条件と比較対象の保険者</t>
+          <t>交付金の交付見込額を保険料収納必要額から控除するか</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節 分析資料</t>
+          <t>計画素案 第6章第6節 将来推計 第3段階 保険料算定式の国の様式との対照</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
@@ -14083,42 +14083,42 @@
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16を代理指標へ振り替えるかどうか</t>
+          <t>日常生活圏域ごとの必要利用定員総数の基盤整備単位、認知症対応型共同生活介護の圏域別の定員</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・資料1 全16KPIの4項目</t>
+          <t>計画素案 第1章第7節・第6章第4節4 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
@@ -14128,42 +14128,42 @@
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項（重大6件）の取扱いと、事業所への照会の要否</t>
+          <t>社会福祉法等の一部を改正する法律による改正の反映（7件）</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>公表資料により確認できるもの（法令）</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第5・6節 H06・H11・H13・H14の基準値</t>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節 ケアプラン点検実施要領</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -14173,22 +14173,22 @@
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>骨子案（章立て・基本理念・基本目標・代表KPIの枠組み）</t>
+          <t>給付適正化計画の位置づけ（案B）の反映内容</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -14198,17 +14198,17 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>骨子案 素案の次稿</t>
+          <t>計画素案 第1章第2節・第5章 基本目標5・資料5 給付適正化計画の位置づけと追加検討事項</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -14218,22 +14218,22 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>策定委員会の開催日程・審議事項・資料提出期限、意見公募手続の期間、町別値の公表基準</t>
+          <t>令和9年4月1日から義務となる2件（協力医療機関の要件・生産性向上の委員会）への対応</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -14243,17 +14243,17 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>委員会資料原案 パブリックコメント資料</t>
+          <t>計画素案 第1章第9節 計画素案 第5章 基本目標3・4 計画素案 第6章第4節3</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H47" s="13" t="inlineStr">
@@ -14263,32 +14263,32 @@
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標のうち「市町村数」を単位とするものの読替えの考え方</t>
+          <t>基盤整備の選択肢として省令上の類型5件を計画に掲げるか</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（北海道）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節 追加調査報告書 04シート</t>
+          <t>計画素案 第6章第4節1 計画素案 第6章第2節2（2） サービス見込量の算定</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
@@ -14308,22 +14308,22 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>各調査の対象者の範囲（母集団が異なる指標を併記する前提）</t>
+          <t>見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート H06・H11の基準値</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節・第3節・第6節</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H49" s="13" t="inlineStr">
@@ -14353,22 +14353,22 @@
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ3件の確認</t>
+          <t>計画素案 第6章第2節の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -14378,17 +14378,17 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>計画素案 第6章第2節2 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H50" s="13" t="inlineStr">
@@ -14398,42 +14398,42 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>基金の積立ての上限の解釈と第10期の取崩方針</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認 02シート 素案 第6章第6節 将来推計 第3段階</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H51" s="13" t="inlineStr">
@@ -14443,22 +14443,22 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティから個人情報を削除する運用</t>
+          <t>単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -14468,17 +14468,17 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録 業務工程管理表</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -14488,22 +14488,22 @@
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -14513,42 +14513,42 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録 業務工程管理表</t>
+          <t>サービス見込量の算定 計画素案 第4章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>最大13円</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎に包括的支援事業費・任意事業費を含めない扱い</t>
+          <t>見込量の伸びにサービス別の趨勢を半分反映するか</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -14558,62 +14558,62 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H54" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>最大58円</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提4件</t>
+          <t>施設及び居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（3町）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート 計画素案 第6章第6節</t>
+          <t>サービス見込量の算定 計画素案 第6章第4節4</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H55" s="13" t="inlineStr">
@@ -14623,22 +14623,22 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -14648,17 +14648,17 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -14668,22 +14668,22 @@
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>給付適正化の効果を見込量に織り込まないこと</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -14693,42 +14693,42 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 計画素案 第6章第4節</t>
+          <t>サービス見込量の算定 計画素案 第5章 基本目標5・第6章第2節</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H57" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応、3町の該当状況調査の回答</t>
+          <t>過年度の趨勢に現れない要因12件の扱い</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H58" s="13" t="inlineStr">
@@ -14758,22 +14758,22 @@
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複の確認を行うか</t>
+          <t>中長期推計をどこまで算定し、どこまで計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08 実施済み3調査の受領点検と集計 06・07</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第2章第8節・第6章第2節</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
@@ -14793,7 +14793,7 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H59" s="13" t="inlineStr">
@@ -14803,32 +14803,32 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法</t>
+          <t>令和9年4月に新設される3区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>公表を待つもの（国の政令・省令）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料 町別データシート 構成町の意見への回答 2・3</t>
+          <t>サービス見込量 第2次概算 計画素案 第1章第9節・第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -14848,32 +14848,32 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>町別データシート 構成町の意見への回答 2</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -14893,32 +14893,32 @@
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律による改正の反映（7件）</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>公表資料により確認できるもの（法令）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節 ケアプラン点検実施要領</t>
+          <t>成果品一覧 送付資料一覧</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H62" s="13" t="inlineStr">
@@ -14938,32 +14938,32 @@
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件（協力医療機関の要件・生産性向上の委員会）への対応</t>
+          <t>施策2-5の代表KPIを施策化への転換率とするか</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節 計画素案 第5章 基本目標3・4 計画素案 第6章第4節3</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H63" s="13" t="inlineStr">
@@ -14983,32 +14983,32 @@
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因12件の扱い</t>
+          <t>地域ケア会議の3町共通の記録様式</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H64" s="13" t="inlineStr">
@@ -15028,22 +15028,22 @@
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧 送付資料一覧</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
@@ -15073,22 +15073,22 @@
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを施策化への転換率とするか</t>
+          <t>地域ケア会議関係資料（転載を禁ずる記載のある2件）の取扱い</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>地域ケア会議の受領点検とKPI設計案 計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
@@ -15118,22 +15118,22 @@
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式</t>
+          <t>見える化システムの推計方式を基本推計とするか</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -15143,7 +15143,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
@@ -15163,32 +15163,32 @@
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合（システムの操作））</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>将来推計 第1段階 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
@@ -15208,22 +15208,22 @@
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式を基本推計とするか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
@@ -15253,32 +15253,32 @@
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="5" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>利用率等の伸びの選択（4つの選択肢のいずれか）</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合（システムの操作））</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階 計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -15298,32 +15298,32 @@
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画の扱い</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H71" s="13" t="inlineStr">
@@ -15343,22 +15343,22 @@
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>概算を既定値のまま出してよいか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>計画素案 第6章第2節・第3節 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
@@ -15378,7 +15378,7 @@
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H72" s="13" t="inlineStr">
@@ -15388,22 +15388,22 @@
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="5" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -15413,7 +15413,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -15423,42 +15423,42 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定（告示後に再算定）</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>町別データシート サービス見込量の算定</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H74" s="13" t="inlineStr">
@@ -15478,22 +15478,22 @@
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="5" t="n">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -15503,7 +15503,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 サービス見込量の算定</t>
+          <t>計画素案 第2章第4節・第4章第3節</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
@@ -15523,42 +15523,42 @@
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>区域を越えた施設利用の扱い、区域外利用の把握の手段</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節 図表集</t>
+          <t>計画素案 第6章第4節4 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H76" s="13" t="inlineStr">
@@ -15568,22 +15568,22 @@
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -15593,17 +15593,17 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標3・資料1 アンケート調査の集計分析報告書 02・14シート</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H77" s="13" t="inlineStr">
@@ -15613,42 +15613,42 @@
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="5" t="n">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東川町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H78" s="13" t="inlineStr">
@@ -15658,22 +15658,22 @@
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="5" t="n">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけと3町展開</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -15683,17 +15683,17 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H79" s="13" t="inlineStr">
@@ -15703,42 +15703,42 @@
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="5" t="n">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（美瑛町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>町別データシート サービス見込量の算定</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -15748,22 +15748,22 @@
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="5" t="n">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -15773,17 +15773,17 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H81" s="13" t="inlineStr">
@@ -15793,22 +15793,22 @@
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -15818,17 +15818,17 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>見える化システムへの入力 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
@@ -15838,42 +15838,42 @@
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="5" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持と担い手の高齢化の状況</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外すか</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東神楽町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -15883,22 +15883,22 @@
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち協議用へ移すもの</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -15908,17 +15908,17 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート 計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>一部解消</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -15928,22 +15928,22 @@
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価を示す図3点を計画本文に掲げるか</t>
+          <t>人口の将来推計の方法を案Cから変化率法に改めるか</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート 計画素案 第3章第4節・資料7</t>
+          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F85" s="13" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -15973,22 +15973,22 @@
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証 07シート 見える化へ入力する箇所と入力値 02シート 計画素案 第2章第1節・第6章第1節</t>
+          <t>計画素案 第2章第1節 図表集</t>
         </is>
       </c>
       <c r="F86" s="13" t="inlineStr">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -16018,22 +16018,22 @@
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
-          <t>通常（2点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列（社人研推計か3町の総合計画か）</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1 アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>3町の第10期計画へ共通指標を掲載することの合意</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東川町）</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2 3町協議資料</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
@@ -16098,7 +16098,7 @@
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -16108,22 +16108,22 @@
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>21</v>
+        <v>161</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様（章別の頁配分・図表の掲載点数・概要版・入稿期限）</t>
+          <t>東川町のチームオレンジ事業の位置づけと3町展開</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部） 概要版</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
@@ -16143,7 +16143,7 @@
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
@@ -16153,32 +16153,32 @@
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提（3案のいずれか）</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（美瑛町）</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 認定者数・給付費の推計</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F90" s="13" t="inlineStr">
@@ -16188,7 +16188,7 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -16198,22 +16198,22 @@
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>給付適正化を第10期に実施するか、推計へ政策効果として見込むか</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章 給付費の推計</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F91" s="13" t="inlineStr">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
@@ -16243,22 +16243,22 @@
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -16268,17 +16268,17 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>計画素案 第6章第4節・第6章第5節 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F92" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H92" s="13" t="inlineStr">
@@ -16288,42 +16288,42 @@
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>利用率等の伸びの選択（4つの選択肢のいずれか）</t>
+          <t>東神楽町の通いの場の維持と担い手の高齢化の状況</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東神楽町）</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H93" s="13" t="inlineStr">
@@ -16333,22 +16333,22 @@
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
@@ -16378,22 +16378,22 @@
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>計画素案に独自に加えた記載のうち協議用へ移すもの</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート 計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
@@ -16423,7 +16423,7 @@
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
@@ -16458,7 +16458,7 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
@@ -16468,22 +16468,22 @@
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応</t>
+          <t>交付金の評価を示す図3点を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -16493,7 +16493,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート 計画素案 資料7／別冊の図表集</t>
+          <t>図表データ管理台帳 03シート 計画素案 第3章第4節・資料7</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
@@ -16503,7 +16503,7 @@
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H97" s="13" t="inlineStr">
@@ -16513,32 +16513,32 @@
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の期限と見込量の区分の扱い</t>
+          <t>計画本文の図と別冊の図表集の対応</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>公表を待つもの（国の告示）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節（2）・第6章第4節1 サービス見込量の算定・見える化システムへの入力値</t>
+          <t>図表データ管理台帳 01シート・02シート 計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H98" s="13" t="inlineStr">
@@ -16558,22 +16558,22 @@
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策（4案のいずれか）</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -16583,17 +16583,17 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節 見込量表（3種別）</t>
+          <t>人口推計コーホート分析の妥当性検証 07シート 見える化へ入力する箇所と入力値 02シート 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H99" s="13" t="inlineStr">
@@ -16609,36 +16609,36 @@
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="5" t="n">
-        <v>25</v>
+        <v>183</v>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの目標値の決定</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの令和11年度目標値</t>
+          <t>夜間対応型訪問介護の経過措置の期限と見込量の区分の扱い</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>公表を待つもの（国の告示）</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・第5章 全16KPIの目標値</t>
+          <t>計画素案 第6章第2節（2）・第6章第4節1 サービス見込量の算定・見える化システムへの入力値</t>
         </is>
       </c>
       <c r="F100" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H100" s="13" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
@@ -17467,7 +17467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17658,26 +17658,26 @@
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -17693,26 +17693,26 @@
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>150</v>
+        <v>96</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
@@ -17722,32 +17722,32 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
+          <t>②　未確定箇所として残す</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>7</v>
+        <v>112</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -17763,26 +17763,26 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>②　未確定箇所として残す</t>
+          <t>③　当該の記載を掲げない（算定しない）</t>
         </is>
       </c>
     </row>
@@ -17842,179 +17842,179 @@
       </c>
       <c r="H17" s="4" t="inlineStr"/>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>広域連合・3町</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+    <row r="18"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4　資料が届かないと計画の記載に跡が残るもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>ご提供をお願いする資料</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>出どころ</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>届かない場合の扱い</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>計画が確定するか</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>3町・事業者</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>優先（8点）</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>④　現に確認できている値で確定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の実績のご提供</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>広域連合・3町</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>②　未確定箇所として残す</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>未確定箇所が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>175</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3町</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>②　未確定箇所として残す</t>
+        </is>
+      </c>
+      <c r="G22" s="19" t="inlineStr">
+        <is>
+          <t>未確定箇所が残る</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>178</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>3町・法令</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>優先（7点）</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>優先（6点）</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>①　安全側の置き方で算定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>4　資料が届かないと計画の記載に跡が残るもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>ご提供をお願いする資料</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>出どころ</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>届かない場合の扱い</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>計画が確定するか</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>②　未確定箇所として残す</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>未確定箇所が残る</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -18030,16 +18030,16 @@
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
+          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -18065,26 +18065,26 @@
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
+          <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>3町・法令</t>
+          <t>北海道・国の政令</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -18100,131 +18100,131 @@
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>179</v>
+        <v>2</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
+          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
         <is>
-          <t>②　未確定箇所として残す</t>
-        </is>
-      </c>
-      <c r="G27" s="19" t="inlineStr">
-        <is>
-          <t>未確定箇所が残る</t>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
+          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
         <is>
-          <t>②　未確定箇所として残す</t>
-        </is>
-      </c>
-      <c r="G28" s="19" t="inlineStr">
-        <is>
-          <t>未確定箇所が残る</t>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
         </is>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>186</v>
+        <v>15</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>特定施設の定義の改正による区域内3施設の扱い</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
+          <t>令和3年度から令和8年度までの各月の認定者数</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>北海道・国の政令</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>②　未確定箇所として残す</t>
-        </is>
-      </c>
-      <c r="G29" s="19" t="inlineStr">
-        <is>
-          <t>未確定箇所が残る</t>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
         </is>
       </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
+          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -18240,21 +18240,21 @@
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
+          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -18275,26 +18275,26 @@
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>令和3年度から令和8年度までの各月の認定者数</t>
+          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -18310,16 +18310,16 @@
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
+          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -18345,21 +18345,21 @@
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
+          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -18380,21 +18380,21 @@
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
+          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -18415,16 +18415,16 @@
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
+          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -18450,21 +18450,21 @@
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
+          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -18485,21 +18485,21 @@
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
+          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -18520,26 +18520,26 @@
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -18555,292 +18555,187 @@
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
+          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
+          <t>3町・事業者</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="inlineStr">
+        <is>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>注　②は計画本文に未確定箇所の記号が残るもの、③は当該の事項について記述が残らないものです。①④は資料が届かなくても計画本文を確定でき、当該の事項についての記述も残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>5　ご提供をお願いする先ごとの件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>お願いする先</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>うち月額に効くもの</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>うち法第117条に関わるもの</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>期限が到来しているもの</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
           <t>広域連合</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="G40" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>広域連合（システムの操作）</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の実績のご提供</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>広域連合・3町</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="G42" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>3町・事業者</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>注　②は計画本文に未確定箇所の記号が残るもの、③は当該の事項について記述が残らないものです。①④は資料が届かなくても計画本文を確定でき、当該の事項についての記述も残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="45"/>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>5　ご提供をお願いする先ごとの件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="4" t="inlineStr"/>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>お願いする先</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>うち月額に効くもの</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>うち法第117条に関わるもの</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>期限が到来しているもの</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr"/>
+      <c r="C45" s="13" t="n">
+        <v>40</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>広域連合を通じて構成3町</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="6" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>広域連合を通じて北海道</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合を通じて国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて構成3町</t>
+          <t>広域連合又は構成3町を通じて事業者</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="F49" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F49" s="13" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>広域連合を通じて北海道</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>広域連合を通じて国民健康保険団体連合会</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="6" t="inlineStr"/>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合又は構成3町を通じて事業者</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D52" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53"/>
-    <row r="54" ht="70" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    </row>
+    <row r="50"/>
+    <row r="51" ht="70" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>注1　資料の受領を待たずに算定は進められます。ただし、保険料の月額に効くものは、資料が届いた後に再算定することとなります。
 注2　介護保険法第117条に関わるものは、資料が届かない場合に計画本文へ未確定箇所の記号が残ります。公表の前に解消を要します。
@@ -18852,13 +18747,13 @@
   <mergeCells count="9">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>63件</t>
+          <t>64件</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>189件</t>
+          <t>190件</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>・広域連合から資料をご提供いただく必要があるものは63件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
+          <t>・広域連合から資料をご提供いただく必要があるものは64件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
     <row r="43" ht="86" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項は189件（うち受託者案で確定したもの173件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
+          <t>注1　確認事項は190件（うち受託者案で確定したもの174件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
 注4　基準日　令和8年10月19日</t>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>96</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>96</v>
@@ -2855,9 +2855,9 @@
           <t>低</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -3530,9 +3530,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
     <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>注1　受領又は解消したものは7件、なおご提供をお待ちしているものは16件です。
+          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは14件です。
 注2　備考に記した確認事項の番号は、起票した時点のものです。
 注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
         </is>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>台帳189件・分類189件・分類にないNo. なし</t>
+          <t>台帳190件・分類190件・分類にないNo. なし</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>63＋7＋3＋96＋20＝189（台帳189）</t>
+          <t>64＋7＋3＋96＋20＝190（台帳190）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>未決173件・既定値のないNo. なし</t>
+          <t>未決174件・既定値のないNo. なし</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>63件／区分A 63件・当たらないNo. なし</t>
+          <t>64件／区分A 64件・当たらないNo. なし</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>23件（受領又は解消7件）</t>
+          <t>23件（受領又は解消9件）</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>57＋6＝63（区分A 63）</t>
+          <t>58＋6＝64（区分A 64）</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>区分A 63件・覆った63件・当たらないもの なし</t>
+          <t>区分A 64件・覆った64件・当たらないもの なし</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>ア 33件／イ 17件／ウ 12件／エ 23件／オ 18件／カ 9件／キ 10件</t>
+          <t>ア 33件／イ 17件／ウ 12件／エ 24件／オ 19件／カ 10件／キ 10件</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月30日 85件／令和8年11月13日 85件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 173件／令和9年3月23日 173件</t>
+          <t>令和8年10月30日 85件／令和8年11月13日 85件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 174件／令和9年3月23日 174件</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>16＋173＝189（台帳 189）</t>
+          <t>16＋174＝190（台帳 190）</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0</v>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>16</v>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1</v>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150</t>
+          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150・190</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -5174,7 +5174,7 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの63件を上回ります。</t>
+          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの64件を上回ります。</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
@@ -5296,7 +5296,7 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
     </row>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>注　区分Aの63件のうち57件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
+          <t>注　区分Aの64件のうち58件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
     <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（122件）は区分Aの63件を上回ります。
+          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（125件）は区分Aの64件を上回ります。
 注2　不足しているのは一次統計ではありません。介護保険事業状況報告（年報・月報）、国勢調査、住民基本台帳、見える化システムの指標、交付金の全国集計、総合事業の実施状況に関する調査はいずれも受領しており、サービス見込量・給付費・保険料の算定はこれらにより行っています。不足しているのは、①3町及び広域連合が事業として行った量・費用の記録、②事業所の定員・稼働の実態、③広域連合の条例・規約及び算定の運用、④既に受領している統計の年次又は区分です。
 注3　性質の判定は件名・確認をお願いする内容・徴求する資料の記述によります。</t>
         </is>
@@ -5745,13 +5745,13 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>2</v>
@@ -5827,13 +5827,13 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" s="13" t="n">
         <v>1</v>
@@ -6146,7 +6146,7 @@
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の189件を上回ります。
+          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の190件を上回ります。
 注2　進捗は作業項目の達成状況による算定です。(11)成果品の帰属及び(12)その他は進捗の対象ではないため「―」です。
 注3　業務内容の記号が付されていない確認事項はありません。確認事項のない業務内容（(11) 成果品の帰属）は掲げていません。
 注4　確認事項が最も多い業務内容は(6) 計画書の作成、進捗が最も低い業務内容は(9) パブリックコメント支援です。ご判断・ご決定を求めるものが49件あり、計画への記載の仕方の決定がここに集まっています。</t>
@@ -6276,14 +6276,14 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>14件（5・6・7・23・34・48・56・58・73・74・90・91）</t>
+          <t>15件（5・6・7・23・34・48・56・58・73・74・90・91）</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -6309,14 +6309,14 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>9件（11・12・13・26・66・76・77・81・184）</t>
+          <t>10件（11・12・13・26・66・76・77・81・184・190）</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -6361,7 +6361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6378,7 +6378,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　広域連合から資料の徴求を要するもの（63件）</t>
+          <t>区分A　広域連合から資料の徴求を要するもの（64件）</t>
         </is>
       </c>
     </row>
@@ -6439,36 +6439,36 @@
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>2</v>
+        <v>190</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>見える化システム B5・B6 の【他地域と比較】の出力における比較地域</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
+          <t>見える化システムのB5・B6を【他地域と比較】で出力した際に比較対象として設定した地域、及び当該の出力の系列が本広域連合を別の基準人口で標準化した値か他の地域の値かの別</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>計画素案 第3章第4節2・認定率の年齢調整分析</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -6478,42 +6478,42 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>通常（0点）</t>
+          <t>通常（1点）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
+          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -6529,11 +6529,11 @@
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
+          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節 追加調査報告書 02シート</t>
+          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -6574,11 +6574,11 @@
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>素案 第3章第4節 追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
@@ -6619,11 +6619,11 @@
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -6633,17 +6633,17 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節 クロス集計表</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -6664,11 +6664,11 @@
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6678,12 +6678,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
+          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節 H14の基準値</t>
+          <t>素案 第2章第4〜6節 クロス集計表</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -6709,26 +6709,26 @@
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>3町・総務省</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節 図1・図2・図3</t>
+          <t>素案 第4章第3節 H14の基準値</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
@@ -6754,26 +6754,26 @@
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・総務省</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
+          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
+          <t>素案 第2章第1節 図1・図2・図3</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -6799,26 +6799,26 @@
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
+          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -6844,31 +6844,31 @@
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>令和3年度から令和8年度までの各月の認定者数</t>
+          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -6889,11 +6889,11 @@
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -6903,17 +6903,17 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
+          <t>令和3年度から令和8年度までの各月の認定者数</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節 保険料算定表</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -6934,31 +6934,31 @@
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
+          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 第6章第3節・第6節 保険料算定表</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -6979,26 +6979,26 @@
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
+          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
@@ -7024,31 +7024,31 @@
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>3町・北海道</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
+          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
+          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -7069,31 +7069,31 @@
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・北海道</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
+          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
+          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -7114,11 +7114,11 @@
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -7128,17 +7128,17 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
+          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
+          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
@@ -7159,11 +7159,11 @@
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
+          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -7204,11 +7204,11 @@
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
+          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
+          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -7249,11 +7249,11 @@
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -7263,17 +7263,17 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
+          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
+          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
@@ -7294,26 +7294,26 @@
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
+          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
+          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -7339,26 +7339,26 @@
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
+          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
+          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -7384,11 +7384,11 @@
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費がどの科目で執行されているか</t>
+          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
+          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -7429,11 +7429,11 @@
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
+          <t>一般介護予防事業費がどの科目で執行されているか</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -7474,11 +7474,11 @@
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
+          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -7519,11 +7519,11 @@
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -7533,12 +7533,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援2事業所ほかの指定の状況</t>
+          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -7564,26 +7564,26 @@
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
+          <t>居宅介護支援2事業所ほかの指定の状況</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
+          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -7609,31 +7609,31 @@
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
+          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
+          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
@@ -7654,26 +7654,26 @@
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
+          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
+          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -7699,26 +7699,26 @@
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
+          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
+          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -7744,26 +7744,26 @@
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
+          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
+          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -7789,26 +7789,26 @@
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
+          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
+          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -7834,26 +7834,26 @@
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>広域連合・国民健康保険団体連合会</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
+          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
+          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -7879,26 +7879,26 @@
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
+          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -7924,11 +7924,11 @@
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
+          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -7969,11 +7969,11 @@
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -7983,12 +7983,12 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
+          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -8014,11 +8014,11 @@
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
+          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
@@ -8059,26 +8059,26 @@
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
+          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -8091,9 +8091,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>最大47円</t>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -8104,26 +8104,26 @@
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
+          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
+          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -8136,9 +8136,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>最大47円</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
@@ -8149,26 +8149,26 @@
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
+          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -8194,26 +8194,26 @@
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
+          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -8239,11 +8239,11 @@
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
+          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
+          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -8284,26 +8284,26 @@
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
+          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -8329,26 +8329,26 @@
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
+          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -8361,9 +8361,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>最大7円</t>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -8374,26 +8374,26 @@
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -8406,9 +8406,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>最大7円</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -8419,26 +8419,26 @@
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
+          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -8464,11 +8464,11 @@
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
+          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
+          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -8509,11 +8509,11 @@
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
+          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -8554,11 +8554,11 @@
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
+          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -8599,26 +8599,26 @@
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -8644,26 +8644,26 @@
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
+          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節</t>
+          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -8689,11 +8689,11 @@
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -8703,12 +8703,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -8734,26 +8734,26 @@
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・項目定義</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 将来推計 第2段階</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -8779,31 +8779,31 @@
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>見える化システムの操作手引・項目定義</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
+          <t>見える化システムへの入力 将来推計 第2段階</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G57" s="13" t="inlineStr">
@@ -8824,26 +8824,26 @@
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座の開催回数・修了者数</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -8869,21 +8869,21 @@
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
+          <t>認知症サポーター養成講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -8914,21 +8914,21 @@
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>東神楽町</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
+          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -8959,31 +8959,31 @@
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
+          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G61" s="13" t="inlineStr">
@@ -9004,31 +9004,31 @@
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
+          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
@@ -9049,31 +9049,31 @@
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>3町・法令</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
+          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -9094,26 +9094,26 @@
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・法令</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
+          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -9139,11 +9139,11 @@
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -9153,12 +9153,12 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
+          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -9184,31 +9184,31 @@
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
+          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
+          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
@@ -9229,51 +9229,96 @@
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>3町・事業者</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H67" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>通常（0点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="5" t="n">
         <v>186</v>
       </c>
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>北海道・国の政令</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節 サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
-      <c r="F67" s="13" t="inlineStr">
+      <c r="F68" s="13" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G67" s="13" t="inlineStr">
+      <c r="G68" s="13" t="inlineStr">
         <is>
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H67" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
         <is>
           <t>通常（0点）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="70" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69" ht="70" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>注1　影響度は、期限、止めている成果物、保険料の月額への効き、法定記載事項であるかどうか、及び決着しない場合の扱いの有無により点を付けたものです。9点以上を至急、6点から8点を優先としています。
 注2　月額への効きは、当該の前提のみを動かした場合の保険料基準額（月額）の変化です。
@@ -9284,8 +9329,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A69:I69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9297,7 +9342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9313,7 +9358,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　資料が届かない場合の扱い（63件）</t>
+          <t>区分A　資料が届かない場合の扱い（64件）</t>
         </is>
       </c>
     </row>
@@ -11568,8 +11613,43 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="104" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム B5・B6 の【他地域と比較】の出力における比較地域</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>④　現に確認できている値で確定する</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>計画本文には</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="104" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>注1　扱いの区分は 01シート の3によります。①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない（算定しない）、④現に確認できている値で確定する、の4つです。
 注2　「代替の出どころ」は、当方の扱いが依っている資料です。公表資料・年報・北海道の名簿・3町の実施報告書・既に受領している資料のいずれかによるものを示しています。
@@ -11580,8 +11660,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A68:H68"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18641,7 +18721,7 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D45" s="13" t="n">
         <v>1</v>

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -1201,7 +1201,7 @@
           <t>注1　確認事項は190件（うち受託者案で確定したもの174件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月19日</t>
+注4　基準日　令和8年10月20日</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2757,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼の台帳（23件）</t>
+          <t>資料提供依頼の台帳（24件）</t>
         </is>
       </c>
     </row>
@@ -3851,10 +3851,55 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは14件です。
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合介護保険条例のうち、第9期の保険料率（16段階）を定める改正後のもの。あわせて、乗率を国の標準より低く定めた経緯を示す資料（議案・提案理由等）があればご提供いただきたい。</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>所得段階と乗率の確定、保険料の算定</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H28" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは15件です。
 注2　備考に記した確認事項の番号は、起票した時点のものです。
 注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
         </is>
@@ -3863,8 +3908,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A29:I29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4268,7 +4313,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>23件（受領又は解消9件）</t>
+          <t>24件（受領又は解消9件）</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -1201,7 +1201,7 @@
           <t>注1　確認事項は190件（うち受託者案で確定したもの174件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月20日</t>
+注4　基準日　令和8年10月21日</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2757,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼の台帳（24件）</t>
+          <t>資料提供依頼の台帳（25件）</t>
         </is>
       </c>
     </row>
@@ -3896,10 +3896,55 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは15件です。
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの事業所分析機能の出力</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの事業所分析機能により、区域内の事業所ごとの従事者数・利用者数・定員充足率の複数年次の推移を出力いただきたい。同機能は令和8年7月31日のバージョンアップで追加されたものである。介護サービス情報公表システムでも事業所ごとの定員・利用者数・従業者数を確認できるが、公表日が事業所ごとに異なるため同じ時点での比較と推移は本機能によらなければ得られない。</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>事業所の定員と稼働の実績、供給の制約（人材）、施設・居住系の実績の減少の読み方</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは16件です。
 注2　備考に記した確認事項の番号は、起票した時点のものです。
 注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
         </is>
@@ -3908,8 +3953,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A30:I30"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A29:I29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4313,7 +4358,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>24件（受領又は解消9件）</t>
+          <t>25件（受領又は解消9件）</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>64件</t>
+          <t>66件</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>190件</t>
+          <t>192件</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>・広域連合から資料をご提供いただく必要があるものは64件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
+          <t>・広域連合から資料をご提供いただく必要があるものは66件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
         </is>
       </c>
     </row>
@@ -1198,10 +1198,10 @@
     <row r="43" ht="86" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項は190件（うち受託者案で確定したもの174件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
+          <t>注1　確認事項は192件（うち受託者案で確定したもの176件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月21日</t>
+注4　基準日　令和8年10月23日</t>
         </is>
       </c>
     </row>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>49</v>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" s="13" t="n">
         <v>49</v>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>96</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F11" s="13" t="n">
         <v>96</v>
@@ -1774,11 +1774,11 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>21件</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1793,8 +1793,8 @@
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>注1　律速は当方の作業の側にはありません。残るのは、資料のご提供と照会という相手のある作業です。このうち計画の記載に跡が残る20件が、公表の前に解消を要するものです。
-注2　本項の20件と、1の意見公募手続の行の15件は数えているものが違います。本項は区分Aのうち扱いが②③であるもの、1の行は区分を問わず既定値によっても未確定箇所の記号が残るものです。扱い③（当該の記載を掲げない）は記号を残さないため1には現れません。</t>
+          <t>注1　律速は当方の作業の側にはありません。残るのは、資料のご提供と照会という相手のある作業です。このうち計画の記載に跡が残る21件が、公表の前に解消を要するものです。
+注2　本項の21件と、1の意見公募手続の行の15件は数えているものが違います。本項は区分Aのうち扱いが②③であるもの、1の行は区分を問わず既定値によっても未確定箇所の記号が残るものです。扱い③（当該の記載を掲げない）は記号を残さないため1には現れません。</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2757,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼の台帳（25件）</t>
+          <t>資料提供依頼の台帳（30件）</t>
         </is>
       </c>
     </row>
@@ -3941,10 +3941,235 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは16件です。
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの地方公共団体向け利用マニュアル</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>地域包括ケア「見える化」システムの地方公共団体向け利用マニュアル（当該年度の全編）をご提供いただきたい。【システム操作編② 将来推計】を含む。ログイン後の「操作に困ったときは」よりダウンロードできる。画面の項目名・選択肢・単位・丸め・空欄と0の扱いを確かめるためのものである。</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>将来推計の入力値、施設・居住系の画面から先へ進めない件</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの第10期新機能の出力</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>第10期の計画策定に向けて追加された機能の出力をご提供いただきたい。①レーダーチャート（3観点×各6指標＝18指標の偏差値及び算出に用いた各指標の値）②介護サービス自給率（給付額全体及びサービス別。時系列推移と地域比較）③人口メッシュ（500mメッシュ別人口と介護施設・事業所の所在及び同心円。令和7年及び令和22年）④将来推計の伸びの比較グラフ（Excel形式）。①②③は現状分析機能、④は将来推計機能による。</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>類似保険者との比較分析、区域外の事業所の利用、日常生活圏域の設定、伸びの選択</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの地域分析・検討シート（比較地域を設定したもの）</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>ダッシュボード機能の専用フォーマット「地域分析・検討シート」について、比較地域に上川管内の保険者又は同様の構成の広域連合を設定したものをご出力いただきたい（表示期間は令和6年度から令和8年度まで）。画面右上の操作メニューからPDF又はExcelで出力できる。</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>類似保険者との比較分析、地域分析・検討シートの記載</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H32" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムのB7・B8（要介護者の状況）の出力</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>B7（認知症高齢者自立度の状況）及びB8（障害高齢者自立度の状況）について、閲覧可能な期間の全件をご出力いただきたい。令和8年10月5日に閲覧可能な期間が追加されている。</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第1節3（認知症高齢者の状況）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>要介護認定適正化事業の業務分析データ</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>国保連合会介護給付適正化システムの業務分析データ（令和6年度から令和8年度まで）をご提供いただきたい。要介護認定の適正化、ケアプランの点検、医療情報との突合、縦覧点検及び介護給付費通知の実施状況に関するもの。厚生労働省 要介護認定適正化事業のページからアクセスでき、自治体ごとに定められた自治体ID及びパスワードを要する。</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>第7期給付適正化計画の主要3事業の基準値、調整交付金の一定の取組による減額の判定</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="H34" s="13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは21件です。
 注2　備考に記した確認事項の番号は、起票した時点のものです。
 注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
         </is>
@@ -3953,7 +4178,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A35:I35"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4033,7 +4258,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>台帳190件・分類190件・分類にないNo. なし</t>
+          <t>台帳192件・分類192件・分類にないNo. なし</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -4083,7 +4308,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>64＋7＋3＋96＋20＝190（台帳190）</t>
+          <t>66＋7＋3＋96＋20＝192（台帳192）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4208,7 +4433,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>未決174件・既定値のないNo. なし</t>
+          <t>未決176件・既定値のないNo. なし</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -4333,7 +4558,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>64件／区分A 64件・当たらないNo. なし</t>
+          <t>66件／区分A 66件・当たらないNo. なし</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
@@ -4358,7 +4583,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>25件（受領又は解消9件）</t>
+          <t>30件（受領又は解消9件）</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -4533,7 +4758,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>58＋6＝64（区分A 64）</t>
+          <t>60＋6＝66（区分A 66）</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -4583,7 +4808,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>区分A 64件・覆った64件・当たらないもの なし</t>
+          <t>区分A 66件・覆った66件・当たらないもの なし</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -4608,7 +4833,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>ア 33件／イ 17件／ウ 12件／エ 24件／オ 19件／カ 10件／キ 10件</t>
+          <t>ア 35件／イ 17件／ウ 12件／エ 26件／オ 19件／カ 10件／キ 10件</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -4708,7 +4933,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月30日 85件／令和8年11月13日 85件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 174件／令和9年3月23日 174件</t>
+          <t>令和8年10月30日 87件／令和8年11月13日 87件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 176件／令和9年3月23日 176件</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -4808,7 +5033,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>16＋174＝190（台帳 190）</t>
+          <t>16＋176＝192（台帳 192）</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -4929,10 +5154,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0</v>
@@ -5075,10 +5300,10 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>16</v>
@@ -5139,7 +5364,7 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1</v>
@@ -5151,7 +5376,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150・190</t>
+          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150・190・191・192</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -5264,7 +5489,7 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの64件を上回ります。</t>
+          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの66件を上回ります。</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5571,7 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -5366,7 +5591,7 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
@@ -5386,7 +5611,7 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
     </row>
@@ -5428,7 +5653,7 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -5463,7 +5688,7 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>注　区分Aの64件のうち58件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
+          <t>注　区分Aの66件のうち60件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5730,7 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
@@ -5565,7 +5790,7 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
@@ -5640,7 +5865,7 @@
     <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（125件）は区分Aの64件を上回ります。
+          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（129件）は区分Aの66件を上回ります。
 注2　不足しているのは一次統計ではありません。介護保険事業状況報告（年報・月報）、国勢調査、住民基本台帳、見える化システムの指標、交付金の全国集計、総合事業の実施状況に関する調査はいずれも受領しており、サービス見込量・給付費・保険料の算定はこれらにより行っています。不足しているのは、①3町及び広域連合が事業として行った量・費用の記録、②事業所の定員・稼働の実態、③広域連合の条例・規約及び算定の運用、④既に受領している統計の年次又は区分です。
 注3　性質の判定は件名・確認をお願いする内容・徴求する資料の記述によります。</t>
         </is>
@@ -5958,13 +6183,13 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>5</v>
@@ -6236,7 +6461,7 @@
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の190件を上回ります。
+          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の192件を上回ります。
 注2　進捗は作業項目の達成状況による算定です。(11)成果品の帰属及び(12)その他は進捗の対象ではないため「―」です。
 注3　業務内容の記号が付されていない確認事項はありません。確認事項のない業務内容（(11) 成果品の帰属）は掲げていません。
 注4　確認事項が最も多い業務内容は(6) 計画書の作成、進捗が最も低い業務内容は(9) パブリックコメント支援です。ご判断・ご決定を求めるものが49件あり、計画への記載の仕方の決定がここに集まっています。</t>
@@ -6333,14 +6558,14 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>25件（15・16・30・36・47・50・52・68・78・82・93・102）</t>
+          <t>27件（15・16・30・36・47・50・52・68・78・82・93・102）</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -6451,7 +6676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6468,7 +6693,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　広域連合から資料の徴求を要するもの（64件）</t>
+          <t>区分A　広域連合から資料の徴求を要するもの（66件）</t>
         </is>
       </c>
     </row>
@@ -6574,36 +6799,36 @@
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
+          <t>見える化システムの「介護保険事業状況報告の設定」の画面において、令和8年度の実績見込みの算定に用いる月として設定されている月（起点及び終期）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -6613,17 +6838,17 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>通常（0点）</t>
+          <t>通常（1点）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>5</v>
+        <v>192</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -6633,22 +6858,22 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
+          <t>見える化システムに現に入力されている地域支援事業費の額と、その額が決算額であるか対象経費支出予定額であるかの別。対象経費支出予定額に改める場合は寄付金その他の収入額及び交付金の対象とならない経費の額</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
+          <t>サービス見込量の算定 計画素案 第6章第3節2・第6章第6節</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -6658,42 +6883,42 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>通常（0点）</t>
+          <t>通常（1点）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
+          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節 追加調査報告書 02シート</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -6709,11 +6934,11 @@
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -6723,12 +6948,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -6754,11 +6979,11 @@
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6768,17 +6993,17 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節 クロス集計表</t>
+          <t>素案 第3章第4節 追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -6799,11 +7024,11 @@
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -6813,17 +7038,17 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節 H14の基準値</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -6844,26 +7069,26 @@
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>3町・総務省</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節 図1・図2・図3</t>
+          <t>素案 第2章第4〜6節 クロス集計表</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -6889,26 +7114,26 @@
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
+          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
+          <t>素案 第4章第3節 H14の基準値</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -6934,26 +7159,26 @@
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>3町・総務省</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
+          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第2章第1節 図1・図2・図3</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -6979,31 +7204,31 @@
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>令和3年度から令和8年度までの各月の認定者数</t>
+          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -7024,31 +7249,31 @@
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
+          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節 保険料算定表</t>
+          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -7069,31 +7294,31 @@
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
+          <t>令和3年度から令和8年度までの各月の認定者数</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -7114,31 +7339,31 @@
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
+          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
+          <t>素案 第6章第3節・第6節 保険料算定表</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -7159,31 +7384,31 @@
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>3町・北海道</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
+          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -7204,26 +7429,26 @@
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
+          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
+          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -7249,26 +7474,26 @@
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・北海道</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
+          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
+          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -7294,11 +7519,11 @@
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -7308,17 +7533,17 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
+          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -7339,11 +7564,11 @@
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -7353,12 +7578,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
+          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
+          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -7384,11 +7609,11 @@
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -7398,17 +7623,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
+          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
+          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -7429,31 +7654,31 @@
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
+          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
+          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -7474,11 +7699,11 @@
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7488,12 +7713,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
+          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
+          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -7519,26 +7744,26 @@
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費がどの科目で執行されているか</t>
+          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
+          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -7564,11 +7789,11 @@
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7578,12 +7803,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
+          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -7609,11 +7834,11 @@
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -7623,12 +7848,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
+          <t>一般介護予防事業費がどの科目で執行されているか</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -7654,11 +7879,11 @@
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -7668,12 +7893,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援2事業所ほかの指定の状況</t>
+          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -7699,26 +7924,26 @@
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
+          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -7744,31 +7969,31 @@
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
+          <t>居宅介護支援2事業所ほかの指定の状況</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
+          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -7789,31 +8014,31 @@
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
+          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
+          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -7834,26 +8059,26 @@
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
+          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
+          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -7879,11 +8104,11 @@
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -7893,12 +8118,12 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
+          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
+          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -7924,26 +8149,26 @@
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
+          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
+          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -7969,26 +8194,26 @@
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>広域連合・国民健康保険団体連合会</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
+          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
+          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -8014,26 +8239,26 @@
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
+          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
+          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -8059,26 +8284,26 @@
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
+          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -8104,11 +8329,11 @@
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -8118,12 +8343,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
+          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
+          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
@@ -8149,11 +8374,11 @@
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -8163,12 +8388,12 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
+          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -8194,26 +8419,26 @@
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
+          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -8226,9 +8451,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>最大47円</t>
+      <c r="H42" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
@@ -8239,11 +8464,11 @@
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -8253,12 +8478,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
+          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -8284,26 +8509,26 @@
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
+          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -8316,9 +8541,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H44" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>最大47円</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -8329,11 +8554,11 @@
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -8343,12 +8568,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
+          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
+          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -8374,26 +8599,26 @@
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
+          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -8419,26 +8644,26 @@
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
+          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
+          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -8464,26 +8689,26 @@
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -8496,9 +8721,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>最大7円</t>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -8509,26 +8734,26 @@
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
+          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -8554,26 +8779,26 @@
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -8586,9 +8811,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H50" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>最大7円</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -8599,26 +8824,26 @@
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
+          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -8644,11 +8869,11 @@
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -8658,12 +8883,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
+          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
+          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -8689,11 +8914,11 @@
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -8703,12 +8928,12 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
+          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -8734,26 +8959,26 @@
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
+          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
+          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -8779,11 +9004,11 @@
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -8793,12 +9018,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -8824,26 +9049,26 @@
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -8869,26 +9094,26 @@
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・項目定義</t>
+          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 将来推計 第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -8914,31 +9139,31 @@
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -8959,31 +9184,31 @@
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座の開催回数・修了者数</t>
+          <t>見える化システムの操作手引・項目定義</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>見える化システムへの入力 将来推計 第2段階</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -9004,26 +9229,26 @@
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -9049,21 +9274,21 @@
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>東神楽町</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
+          <t>認知症サポーター養成講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -9094,31 +9319,31 @@
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
+          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
@@ -9139,31 +9364,31 @@
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
+          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -9184,31 +9409,31 @@
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>3町・法令</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
+          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -9229,31 +9454,31 @@
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
+          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -9274,26 +9499,26 @@
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・法令</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
+          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -9319,31 +9544,31 @@
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
+          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
+          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
@@ -9364,51 +9589,141 @@
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>3町</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H68" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>通常（0点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>3町・事業者</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H69" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>通常（0点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="5" t="n">
         <v>186</v>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>北海道・国の政令</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節 サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
-      <c r="F68" s="13" t="inlineStr">
+      <c r="F70" s="13" t="inlineStr">
         <is>
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G70" s="13" t="inlineStr">
         <is>
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H68" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="H70" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
         <is>
           <t>通常（0点）</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="70" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71" ht="70" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>注1　影響度は、期限、止めている成果物、保険料の月額への効き、法定記載事項であるかどうか、及び決着しない場合の扱いの有無により点を付けたものです。9点以上を至急、6点から8点を優先としています。
 注2　月額への効きは、当該の前提のみを動かした場合の保険料基準額（月額）の変化です。
@@ -9420,7 +9735,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A71:I71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9432,7 +9747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9448,7 +9763,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　資料が届かない場合の扱い（64件）</t>
+          <t>区分A　資料が届かない場合の扱い（66件）</t>
         </is>
       </c>
     </row>
@@ -11738,8 +12053,78 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="104" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="42" customHeight="1">
+      <c r="A70" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>④　現に確認できている値で確定する</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
+        </is>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="104" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>注1　扱いの区分は 01シート の3によります。①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない（算定しない）、④現に確認できている値で確定する、の4つです。
 注2　「代替の出どころ」は、当方の扱いが依っている資料です。公表資料・年報・北海道の名簿・3町の実施報告書・既に受領している資料のいずれかによるものを示しています。
@@ -11750,8 +12135,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17637,7 +18022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -18758,80 +19143,95 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの「介護保険事業状況報告の設定」の画面において、令和8年度の実績見込みの算定に用いる月として設定されている月（起点及び終期）</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="inlineStr">
+        <is>
+          <t>③　当該の記載を掲げない（算定しない）</t>
+        </is>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t>確定できる</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>注　②は計画本文に未確定箇所の記号が残るもの、③は当該の事項について記述が残らないものです。①④は資料が届かなくても計画本文を確定でき、当該の事項についての記述も残ります。</t>
         </is>
       </c>
     </row>
-    <row r="42"/>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="43"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>5　ご提供をお願いする先ごとの件数</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="4" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>お願いする先</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>うち月額に効くもの</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>うち法第117条に関わるもの</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>期限が到来しているもの</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="6" t="inlineStr"/>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>広域連合</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="n">
-        <v>41</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>39</v>
-      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて構成3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>1</v>
@@ -18840,72 +19240,92 @@
         <v>3</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて北海道</t>
+          <t>広域連合を通じて構成3町</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて国民健康保険団体連合会</t>
+          <t>広域連合を通じて北海道</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="13" t="n">
         <v>1</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>0</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>広域連合又は構成3町を通じて事業者</t>
+          <t>広域連合を通じて国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="F49" s="13" t="n">
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="6" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>広域連合又は構成3町を通じて事業者</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51" ht="70" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="51"/>
+    <row r="52" ht="70" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>注1　資料の受領を待たずに算定は進められます。ただし、保険料の月額に効くものは、資料が届いた後に再算定することとなります。
 注2　介護保険法第117条に関わるものは、資料が届かない場合に計画本文へ未確定箇所の記号が残ります。公表の前に解消を要します。
@@ -18917,12 +19337,12 @@
   <mergeCells count="9">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
+++ b/output/第10期計画_確認事項の資料徴求と公表資料による確認.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>66件</t>
+          <t>64件</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>6件</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>96件</t>
+          <t>97件</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>23件</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       <c r="C11" s="8" t="inlineStr"/>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>192件</t>
+          <t>193件</t>
         </is>
       </c>
     </row>
@@ -795,21 +795,21 @@
     <row r="14" ht="48" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>・広域連合から資料をご提供いただく必要があるものは66件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
+          <t>・広域連合から資料をご提供いただく必要があるものは64件です。うち2件は保険料の月額に効き、4件は介護保険法第117条（計画の記載事項・手続）に関わります。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="48" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>・公表資料により確認できるものは7件です。当方の作業環境は外部の情報提供サイトへ接続できないため、公表資料であっても写しのご提供をお願いすることになります。ほかに3件は国の政令・省令・告示の公表を待つものであり、ご提供をお願いできるものではありません。</t>
+          <t>・公表資料により確認できるものは6件です。当方の作業環境は外部の情報提供サイトへ接続できないため、公表資料であっても写しのご提供をお願いすることになります。ほかに3件は国の政令・省令・告示の公表を待つものであり、ご提供をお願いできるものではありません。</t>
         </is>
       </c>
     </row>
     <row r="16" ht="48" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>・96件は資料ではなくご判断・ご決定をお願いするものです。資料をいただいても決着しません。うち18件は、ご判断の前提として資料又は事実の確認を併せて要します。残る20件は資料の徴求を要しないもの（既に決着したもの及び当方の作業により確認できるもの）です。</t>
+          <t>・97件は資料ではなくご判断・ご決定をお願いするものです。資料をいただいても決着しません。うち18件は、ご判断の前提として資料又は事実の確認を併せて要します。残る23件は資料の徴求を要しないもの（既に決着したもの及び当方の作業により確認できるもの）です。</t>
         </is>
       </c>
     </row>
@@ -1198,10 +1198,10 @@
     <row r="43" ht="86" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項は192件（うち受託者案で確定したもの176件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
+          <t>注1　確認事項は193件（うち受託者案で確定したもの174件）です。件数・期限・確認先・状態はいずれも業務工程管理表の一覧によります。
 注2　「資料が届かない場合の扱い」は、令和8年10月19日のご了承により受託者案として採ることとされたものです。本表の区分は「何をすれば決着するか（資料の徴求を要するか）」を示すものであり、ご了承の前後で変わりません。
 注3　区分Aのうち出どころが北海道であるものは、広域連合を通じてご照会をお願いするものです。
-注4　基準日　令和8年10月23日</t>
+注4　基準日　令和8年10月24日</t>
         </is>
       </c>
     </row>
@@ -1346,13 +1346,13 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F6" s="13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="13" t="n">
         <v>7</v>
@@ -1378,13 +1378,13 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>7</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>6</v>
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G10" s="13" t="n">
         <v>7</v>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>7</v>
@@ -1774,11 +1774,11 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>21件</t>
+          <t>20件</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -1793,8 +1793,8 @@
     <row r="26" ht="70" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>注1　律速は当方の作業の側にはありません。残るのは、資料のご提供と照会という相手のある作業です。このうち計画の記載に跡が残る21件が、公表の前に解消を要するものです。
-注2　本項の21件と、1の意見公募手続の行の15件は数えているものが違います。本項は区分Aのうち扱いが②③であるもの、1の行は区分を問わず既定値によっても未確定箇所の記号が残るものです。扱い③（当該の記載を掲げない）は記号を残さないため1には現れません。</t>
+          <t>注1　律速は当方の作業の側にはありません。残るのは、資料のご提供と照会という相手のある作業です。このうち計画の記載に跡が残る20件が、公表の前に解消を要するものです。
+注2　本項の20件と、1の意見公募手続の行の14件は数えているものが違います。本項は区分Aのうち扱いが②③であるもの、1の行は区分を問わず既定値によっても未確定箇所の記号が残るものです。扱い③（当該の記載を掲げない）は記号を残さないため1には現れません。</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2106,7 +2106,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>決着した確認事項（16件）</t>
+          <t>決着した確認事項（19件）</t>
         </is>
       </c>
     </row>
@@ -2612,31 +2612,31 @@
     </row>
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>全国自治体共通版の入力シート・手順書を本件に用いるか</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>了承済</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>令和8年9月18日</t>
+          <t>令和8年10月15日</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>(5)・(7)</t>
+          <t>(2)・(6)</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>全国自治体共通版の入力シート及び手順書はそのまま用いず、当方の試算によることとなった。記載の借用も行わない。これにより、同シートが担当者名及び連絡先を求める欄についての手当ては要しないこととなった。なお所得段階別13段階の推計（確認No.156）及び令和12・27・32年度の算定（確認No.157）は、見える化システム自体が求めるものであるため残り、いずれも当方で算定して解消した</t>
+          <t>認知症施策推進計画の位置づけと見込量への反映 01・09シート【令和8年10月15日】参照条文（001685804）には認知症基本法が収録されていないため、本件は進んでいない。【令和8年10月20日】認知症基本法の条文は原典（e-Gov法令検索）により確認した。第3条（基本理念7号）、第11条（国）、第12条（都道府県）、第13条（市町村。第1項は努力義務、第2項は調和、第3項は第12条第3項から第7項までを準用）である。…</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
@@ -2647,31 +2647,31 @@
     </row>
     <row r="19" ht="58" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較と団体名の扱い</t>
+          <t>全国自治体共通版の入力シート・手順書を本件に用いるか</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>了承済</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>令和8年9月29日</t>
+          <t>令和8年9月18日</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>(2)・(6)</t>
+          <t>(5)・(7)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月29日に令和6・7・8年度の原本を受領し、3か年の比較を終えた。団体名の扱いについて同日ご指示をいただいた。協議用の資料には団体名を掲げてよく、計画素案には掲げない。掲げてよいこととなった場合は協議用の様式を計画に流用する。計画素案に他の団体の名が現れないことは成果品の自己点検で確かめている。なお他の保険者が策定した計画を参照して必要項目を導くことはご指示により行わない。代わりに評価指標の明細列と全国該当率による「全国の標準」から導いている</t>
+          <t>全国自治体共通版の入力シート及び手順書はそのまま用いず、当方の試算によることとなった。記載の借用も行わない。これにより、同シートが担当者名及び連絡先を求める欄についての手当ては要しないこととなった。なお所得段階別13段階の推計（確認No.156）及び令和12・27・32年度の算定（確認No.157）は、見える化システム自体が求めるものであるため残り、いずれも当方で算定して解消した</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -2682,41 +2682,146 @@
     </row>
     <row r="20" ht="58" customHeight="1">
       <c r="A20" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>同様の構成の団体との比較と団体名の扱い</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>令和8年9月29日</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>(2)・(6)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月29日に令和6・7・8年度の原本を受領し、3か年の比較を終えた。団体名の扱いについて同日ご指示をいただいた。協議用の資料には団体名を掲げてよく、計画素案には掲げない。掲げてよいこととなった場合は協議用の様式を計画に流用する。計画素案に他の団体の名が現れないことは成果品の自己点検で確かめている。なお他の保険者が策定した計画を参照して必要項目を導くことはご指示により行わない。代わりに評価指標の明細列と全国該当率による「全国の標準」から導いている</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="5" t="n">
         <v>181</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>介護保険法第117条ほか関係法令の条文のご提供</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>令和8年10月15日</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>(1)・(6)</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>参照条文（001685804）の文字起こしのご提供を受け、介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した。改正されない項（第4項 作成の基準、第6項 加齢に伴う特性への留意、第7項 市町村老人福祉計画と一体、第10項 他計画との整合性の確保、第11項 他計画との調和、第12項 被保険者の意見の反映、第14項 都道府県知事への提出）の項番号が確定した。新旧対照条文と重なる6件の突合はいずれも一致した。…</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>D　資料の徴求を要しないもの</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月23日</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>利用マニュアル【システム操作編② 将来推計】第11.0版により、システムは令和6年度を年報、令和7年度以降を月報により置き、令和7年度は報告月 令和7年5月から令和8年4月まで（令和7年3月サービス分から令和8年2月サービス分まで）の12か月、令和8年度は令和8年5月報告（令和8年3月サービス分）以降を用いることを確かめた。あわせて受領した画面の写し（推計名1006）により、令和8年度は5月・6月・7月の3か月が設定されていることを確かめた。…</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>令和8年10月23日</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>利用マニュアル【システム操作編② 将来推計】第11.0版により、入力する事業費が「総事業費から寄付金その他の収入額を差し引いた額のうち、交付金対象経費として支出する見込みの額（対象経費支出予定額）」であることを確かめた。当方の額は令和6年度決算の款4の額から2事業を除いたものであり、寄付金その他の収入額を差し引いていない点で範囲が異なる。受領した推計結果（推計名1006）は地域支援事業費が全ての欄で0であり、システム上はなお未入力である。…</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>D　資料の徴求を要しないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>注1　「何により決着したか」は回答・対応の欄の記述によります。長いものは句点で切っています。
 注2　決着の日付は回答・対応の欄に記された日付です。記載がないもの（No.49）は「―」としています。
@@ -2726,7 +2831,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A24:G24"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -2740,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2757,7 +2862,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料提供依頼の台帳（30件）</t>
+          <t>資料提供依頼の台帳（31件）</t>
         </is>
       </c>
     </row>
@@ -3935,9 +4040,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I29" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I29" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -3980,9 +4085,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="I30" s="18" t="inlineStr">
+        <is>
+          <t>受領済</t>
         </is>
       </c>
     </row>
@@ -4166,10 +4271,55 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>注1　受領又は解消したものは9件、なおご提供をお待ちしているものは21件です。
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>第10期必要入所（利用）定員、入居定員総数調査票</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>厚生労働省より別途配布されている「第10期必要入所（利用）定員、入居定員総数調査票」（市区町村版）をご提供いただきたい。ファイル内に「保険者用（作業用）」シートがある。見える化システムの「都道府県への提出」画面で、推計データに添付して登録するものである。</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第4節4（必要利用定員総数）、日常生活圏域ごとの必要利用定員総数の様式</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>注1　受領又は解消したものは11件、なおご提供をお待ちしているものは20件です。
 注2　備考に記した確認事項の番号は、起票した時点のものです。
 注3　台帳を1つに減らしていません。確認事項の一覧は計画素案の章節から引く索引として、資料提供依頼の台帳は資料の受領の状況を追うものとして用途が異なるためです。</t>
         </is>
@@ -4178,7 +4328,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4258,7 +4408,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>台帳192件・分類192件・分類にないNo. なし</t>
+          <t>台帳193件・分類193件・分類にないNo. なし</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
@@ -4308,7 +4458,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>66＋7＋3＋96＋20＝192（台帳192）</t>
+          <t>64＋6＋3＋97＋23＝193（台帳193）</t>
         </is>
       </c>
       <c r="E7" s="18" t="inlineStr">
@@ -4433,7 +4583,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>未決176件・既定値のないNo. なし</t>
+          <t>未決174件・既定値のないNo. なし</t>
         </is>
       </c>
       <c r="E12" s="18" t="inlineStr">
@@ -4483,7 +4633,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>決着済み16件・区分Dに入っていないNo. なし</t>
+          <t>決着済み19件・区分Dに入っていないNo. なし</t>
         </is>
       </c>
       <c r="E14" s="18" t="inlineStr">
@@ -4558,7 +4708,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>66件／区分A 66件・当たらないNo. なし</t>
+          <t>64件／区分A 64件・当たらないNo. なし</t>
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
@@ -4583,7 +4733,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>30件（受領又は解消9件）</t>
+          <t>31件（受領又は解消11件）</t>
         </is>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -4758,7 +4908,7 @@
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>60＋6＝66（区分A 66）</t>
+          <t>58＋6＝64（区分A 64）</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
@@ -4808,7 +4958,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>区分A 66件・覆った66件・当たらないもの なし</t>
+          <t>区分A 64件・覆った64件・当たらないもの なし</t>
         </is>
       </c>
       <c r="E27" s="18" t="inlineStr">
@@ -4833,7 +4983,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>ア 35件／イ 17件／ウ 12件／エ 26件／オ 19件／カ 10件／キ 10件</t>
+          <t>ア 33件／イ 17件／ウ 12件／エ 24件／オ 19件／カ 10件／キ 10件</t>
         </is>
       </c>
       <c r="E28" s="18" t="inlineStr">
@@ -4933,7 +5083,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月30日 87件／令和8年11月13日 87件／令和9年1月 15件／令和9年2月19日 7件／令和9年3月3日 176件／令和9年3月23日 176件</t>
+          <t>令和8年10月30日 86件／令和8年11月13日 86件／令和9年1月 14件／令和9年2月19日 7件／令和9年3月3日 174件／令和9年3月23日 174件</t>
         </is>
       </c>
       <c r="E32" s="18" t="inlineStr">
@@ -4983,7 +5133,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>決着16件・区分Dでないもの なし</t>
+          <t>決着19件・区分Dでないもの なし</t>
         </is>
       </c>
       <c r="E34" s="18" t="inlineStr">
@@ -5033,7 +5183,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>16＋176＝192（台帳 192）</t>
+          <t>19＋174＝193（台帳 193）</t>
         </is>
       </c>
       <c r="E36" s="18" t="inlineStr">
@@ -5154,10 +5304,10 @@
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0</v>
@@ -5184,10 +5334,10 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>0</v>
@@ -5199,7 +5349,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -5244,10 +5394,10 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>0</v>
@@ -5274,13 +5424,13 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D10" s="13" t="n">
         <v>4</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>0</v>
@@ -5300,13 +5450,13 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" s="14" t="n">
         <v>7</v>
@@ -5315,7 +5465,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12"/>
@@ -5364,7 +5514,7 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D15" s="13" t="n">
         <v>1</v>
@@ -5376,7 +5526,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150・190・191・192</t>
+          <t>5・6・7・9・10・13・15・16・23・27・30・34・36・47・48・50・52・56・58・66・68・73・76・81・82・90・91・92・95・99・102・112・123・124・125・132・136・138・148・150・190</t>
         </is>
       </c>
       <c r="G15" s="11" t="n"/>
@@ -5489,7 +5639,7 @@
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの66件を上回ります。</t>
+          <t>注　出どころが複数にわたるものは、それぞれの行に数えています（例　給付実績の明細情報は広域連合と国民健康保険団体連合会の双方の行に現れます）。このため件数の和は区分Aの64件を上回ります。</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5721,7 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
@@ -5591,7 +5741,7 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
@@ -5611,7 +5761,7 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
     </row>
@@ -5653,7 +5803,7 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
@@ -5688,7 +5838,7 @@
     <row r="34" ht="34" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>注　区分Aの66件のうち60件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
+          <t>注　区分Aの64件のうち58件は、資料が届かなくても計画本文を確定できます。残る6件は未確定箇所の記号が残るため、公表の前に解消を要します。</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5880,7 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
@@ -5790,7 +5940,7 @@
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
@@ -5865,7 +6015,7 @@
     <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（129件）は区分Aの66件を上回ります。
+          <t>注1　一つの確認事項が複数の性質にわたるため、それぞれの行に数えています。このため件数の和（125件）は区分Aの64件を上回ります。
 注2　不足しているのは一次統計ではありません。介護保険事業状況報告（年報・月報）、国勢調査、住民基本台帳、見える化システムの指標、交付金の全国集計、総合事業の実施状況に関する調査はいずれも受領しており、サービス見込量・給付費・保険料の算定はこれらにより行っています。不足しているのは、①3町及び広域連合が事業として行った量・費用の記録、②事業所の定員・稼働の実態、③広域連合の条例・規約及び算定の運用、④既に受領している統計の年次又は区分です。
 注3　性質の判定は件名・確認をお願いする内容・徴求する資料の記述によります。</t>
         </is>
@@ -6063,19 +6213,19 @@
         <v>37</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>15</v>
       </c>
       <c r="F7" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="13" t="n">
         <v>14</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="13" t="n">
         <v>0</v>
@@ -6186,10 +6336,10 @@
         <v>77</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="13" t="n">
         <v>5</v>
@@ -6198,7 +6348,7 @@
         <v>36</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I10" s="13" t="n">
         <v>6</v>
@@ -6224,7 +6374,7 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>76</v>
@@ -6233,13 +6383,13 @@
         <v>20</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="13" t="n">
         <v>5</v>
@@ -6461,10 +6611,10 @@
     <row r="17" ht="104" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の192件を上回ります。
+          <t>注1　確認事項が複数の業務内容にわたるものは、それぞれの行に数えています。このため件数の和は確認事項の193件を上回ります。
 注2　進捗は作業項目の達成状況による算定です。(11)成果品の帰属及び(12)その他は進捗の対象ではないため「―」です。
 注3　業務内容の記号が付されていない確認事項はありません。確認事項のない業務内容（(11) 成果品の帰属）は掲げていません。
-注4　確認事項が最も多い業務内容は(6) 計画書の作成、進捗が最も低い業務内容は(9) パブリックコメント支援です。ご判断・ご決定を求めるものが49件あり、計画への記載の仕方の決定がここに集まっています。</t>
+注4　確認事項が最も多い業務内容は(6) 計画書の作成、進捗が最も低い業務内容は(9) パブリックコメント支援です。ご判断・ご決定を求めるものが50件あり、計画への記載の仕方の決定がここに集まっています。</t>
         </is>
       </c>
     </row>
@@ -6525,7 +6675,7 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>76</v>
@@ -6537,7 +6687,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>49件</t>
+          <t>50件</t>
         </is>
       </c>
       <c r="G21" s="11" t="n"/>
@@ -6561,11 +6711,11 @@
         <v>77</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>27件（15・16・30・36・47・50・52・68・78・82・93・102）</t>
+          <t>25件（15・16・30・36・47・50・52・68・78・82・93・102）</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -6594,7 +6744,7 @@
         <v>37</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
@@ -6676,7 +6826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -6693,7 +6843,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　広域連合から資料の徴求を要するもの（66件）</t>
+          <t>区分A　広域連合から資料の徴求を要するもの（64件）</t>
         </is>
       </c>
     </row>
@@ -6799,36 +6949,36 @@
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>191</v>
+        <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの「介護保険事業状況報告の設定」の画面において、令和8年度の実績見込みの算定に用いる月として設定されている月（起点及び終期）</t>
+          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
@@ -6838,17 +6988,17 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>192</v>
+        <v>5</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -6858,22 +7008,22 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムに現に入力されている地域支援事業費の額と、その額が決算額であるか対象経費支出予定額であるかの別。対象経費支出予定額に改める場合は寄付金その他の収入額及び交付金の対象とならない経費の額</t>
+          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第3節2・第6章第6節</t>
+          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
@@ -6883,42 +7033,42 @@
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
-          <t>通常（1点）</t>
+          <t>通常（0点）</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の時期と手続、及び制度の適用の単位</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>素案 第3章第4節 追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
@@ -6934,11 +7084,11 @@
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -6948,12 +7098,12 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績、事業量、対象実人数、予算・決算（5区分14項目）</t>
+          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節 妥当性検証報告書 12シート</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -6979,11 +7129,11 @@
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -6993,17 +7143,17 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4年度から令和7年度分）</t>
+          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節 追加調査報告書 02シート</t>
+          <t>素案 第2章第4〜6節 クロス集計表</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -7024,11 +7174,11 @@
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -7038,17 +7188,17 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第9期の代表KPIの実績を算定した資料、運営協議会への報告、北海道への報告の実績</t>
+          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>素案 第4章第3節 H14の基準値</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -7069,26 +7219,26 @@
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・総務省</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>4調査の対象者の範囲、配布数、回収数、回収率</t>
+          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節 クロス集計表</t>
+          <t>素案 第2章第1節 図1・図2・図3</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -7114,26 +7264,26 @@
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>各年9月30日現在の在籍者数、年間の採用者数・退職者数</t>
+          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節 H14の基準値</t>
+          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -7159,26 +7309,26 @@
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>3町・総務省</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>町別・年齢4区分別の住民基本台帳人口（各年10月1日現在）、令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節 図1・図2・図3</t>
+          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
@@ -7204,31 +7354,31 @@
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>6圏域別の面積・人口・認定者数・給付費、小学校区と6圏域の対応</t>
+          <t>令和3年度から令和8年度までの各月の認定者数</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章 圏域別分析資料 調査クロス集計・分析 01・18シート</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G15" s="13" t="inlineStr">
@@ -7249,31 +7399,31 @@
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>中山間地域等に係る加算の算定事業所と件数、3町の除雪計画</t>
+          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節 追加調査報告書 03シート 住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第6章第3節・第6節 保険料算定表</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -7294,31 +7444,31 @@
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>令和3年度から令和8年度までの各月の認定者数</t>
+          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -7339,31 +7489,31 @@
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>基金残高の推移と取崩実績、保険料収納率、所得段階別被保険者数、地域支援事業費の区分別内訳</t>
+          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節 保険料算定表</t>
+          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -7384,31 +7534,31 @@
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>3町・北海道</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>上川中部高齢者保健福祉圏域に関する調整方針、圏域連絡協議会の資料</t>
+          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -7429,26 +7579,26 @@
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>地域密着型通所介護の定員・登録者数・延べ利用者数、施設及び居住系サービスの入所者数・空床・休止床</t>
+          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節 図21・図22</t>
+          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -7474,26 +7624,26 @@
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>3町・北海道</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>認知症初期集中支援チームの訪問実績ほか、医療側からの連携の実施状況</t>
+          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5 図表集 認知症・医療連携</t>
+          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -7519,11 +7669,11 @@
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -7533,17 +7683,17 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の有効回答数（指標別）と集計表</t>
+          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート 素案 第2章第4節</t>
+          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -7564,11 +7714,11 @@
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -7578,12 +7728,12 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けて集計した要介護度の変化（認定の推移の集計）</t>
+          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提 保険料と施策評価の他団体比較 05シート</t>
+          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -7609,11 +7759,11 @@
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -7623,17 +7773,17 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率1.63の設定の経緯（第8期の算定資料）</t>
+          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計 保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G24" s="13" t="inlineStr">
@@ -7654,31 +7804,31 @@
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績、保険料収納率、公費軽減の対象者数</t>
+          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計 保険料の算定 素案 第6章第7節</t>
+          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G25" s="13" t="inlineStr">
@@ -7699,11 +7849,11 @@
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -7713,12 +7863,12 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和7年度分の実績値シート、美瑛町の入力の確認</t>
+          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート 将来推計 第3段階</t>
+          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -7744,26 +7894,26 @@
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査の令和7年度分の写し、生活支援コーディネーターの記入欄の違い</t>
+          <t>一般介護予防事業費がどの科目で執行されているか</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検 素案 第3章第1節・第2節 H05の基準値</t>
+          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -7789,11 +7939,11 @@
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -7803,12 +7953,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>年報（令和7年度）の様式4ほか（令和7年度末の基金残高）</t>
+          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 将来推計 第3段階 素案 第6章第3節・第6節</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -7834,11 +7984,11 @@
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -7848,12 +7998,12 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>一般介護予防事業費がどの科目で執行されているか</t>
+          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート 素案 第6章第3節・第6節</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -7879,11 +8029,11 @@
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -7893,12 +8043,12 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>要介護認定 集計帳票の令和3年度から令和5年度分</t>
+          <t>居宅介護支援2事業所ほかの指定の状況</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -7924,26 +8074,26 @@
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の事業所の撤退・休止の別と時期</t>
+          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -7969,31 +8119,31 @@
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>居宅介護支援2事業所ほかの指定の状況</t>
+          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 3町の社会資源一覧との突合 06シート 計画素案 第2章第3節</t>
+          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
@@ -8014,31 +8164,31 @@
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力（第1号被保険者数を案Cの値に差し替えたもの）</t>
+          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 01シート 算定方法の整合確認 04シート・07シート 計画素案 第6章第3節</t>
+          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
@@ -8059,26 +8209,26 @@
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>要介護認定の適正化の実施状況、美瑛町2事業所の指定の状況</t>
+          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案） 計画素案 第5章 基本目標5</t>
+          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -8104,11 +8254,11 @@
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -8118,12 +8268,12 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集の実施状況</t>
+          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9 計画素案 第5章 基本目標5</t>
+          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
@@ -8149,26 +8299,26 @@
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>介護リームスからの抽出（75歳以上の新規認定者数の年齢階級別・過年度分）</t>
+          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 図表集31シート</t>
+          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -8194,26 +8344,26 @@
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>広域連合・国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥（採用率と離職率の差）の団体別の値</t>
+          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1 内部確認結果への対応整理 04</t>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -8239,26 +8389,26 @@
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期と反映の状況</t>
+          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節 将来推計 第2・第3段階</t>
+          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -8284,26 +8434,26 @@
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>広域連合・国民健康保険団体連合会</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>給付実績（明細情報）から業務継続計画未策定減算の算定事業所を抽出できるか</t>
+          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1 給付実績データの受領点検 05 内部確認結果への対応整理 04・09</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -8329,11 +8479,11 @@
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -8343,12 +8493,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>規約による負担割合又は按分の方法、一般会計繰入金のうち85,652,820円の款項</t>
+          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26） 構成町の意見への回答 4</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
@@ -8374,11 +8524,11 @@
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -8388,12 +8538,12 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）、前回調査の指標別の分母及び集計条件</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート 計画素案 第5章 基本目標5・第2章第4節 アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -8419,26 +8569,26 @@
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等の実施の有無・方法・件数</t>
+          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート 計画素案 第5章 基本目標5</t>
+          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -8451,9 +8601,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>最大47円</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
@@ -8464,11 +8614,11 @@
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -8478,12 +8628,12 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の有無と件数</t>
+          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート 計画素案 第5章 基本目標5</t>
+          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -8509,26 +8659,26 @@
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>給付適正化主要3事業の取組状況が財政調整交付金の算定にどのように反映されるか（北海道へのご照会）</t>
+          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 計画素案 第6章第6節 サービス見込量 第2次概算</t>
+          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -8541,9 +8691,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>最大47円</t>
+      <c r="H44" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
@@ -8554,11 +8704,11 @@
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -8568,12 +8718,12 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>指定地域密着型サービス及び指定地域密着型介護予防サービスの基準を定める条例の全文</t>
+          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理 計画素案 第6章第4節</t>
+          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -8599,26 +8749,26 @@
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護7事業所の共同生活住居数、グループホーム くるみの郷の定員</t>
+          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6 計画素案 第6章第4節4 地域密着型サービス基準省令の論点整理</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -8644,26 +8794,26 @@
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>小規模多機能型居宅介護の定員超過の特例の認定の有無</t>
+          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節 計画素案 第6章第2節2（2） 地域密着型サービス基準省令の論点整理</t>
+          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -8689,26 +8839,26 @@
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数、予防訪問看護の計上</t>
+          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節2</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -8721,9 +8871,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H48" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>最大7円</t>
         </is>
       </c>
       <c r="I48" s="13" t="inlineStr">
@@ -8734,26 +8884,26 @@
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>対計画比の補正で解消しない6件の理由（事業所の休廃止・定員の縮小・空床利用の運用ほか）</t>
+          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算 計画素案 第6章第2節2</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -8779,26 +8929,26 @@
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の事業ごとの利用者実人数（年間）と事業費</t>
+          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節</t>
+          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -8811,9 +8961,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>最大7円</t>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I50" s="13" t="inlineStr">
@@ -8824,26 +8974,26 @@
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の実績7項目（令和6年度から令和8年度）</t>
+          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -8869,11 +9019,11 @@
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -8883,12 +9033,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の画面の状態（空欄の有無・前段の設定の保存の有無）</t>
+          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階 サービス見込量の算定</t>
+          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -8914,11 +9064,11 @@
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -8928,12 +9078,12 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びのパターンを比較する参考シート</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節・第4節</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -8959,26 +9109,26 @@
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率20.84％の分子及び分母</t>
+          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節 将来推計 第1段階・第2段階</t>
+          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -9004,11 +9154,11 @@
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -9018,12 +9168,12 @@
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値</t>
+          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>将来推計 第2段階 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -9049,26 +9199,26 @@
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>3町・事業者</t>
+          <t>広域連合（システムの操作）</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少の事情（休止床・改修・職員の不足の有無）</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第4節2</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -9094,26 +9244,26 @@
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度の整数の作り（保険者単位か3町合計か・時点）</t>
+          <t>見える化システムの操作手引・項目定義</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 計画素案 第6章第2節</t>
+          <t>見える化システムへの入力 将来推計 第2段階</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -9139,31 +9289,31 @@
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>広域連合（システムの操作）</t>
+          <t>広域連合・3町</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>認知症総合支援事業の6事業別の事業費</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G58" s="13" t="inlineStr">
@@ -9184,31 +9334,31 @@
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>東川町</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・項目定義</t>
+          <t>認知症サポーター養成講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 将来推計 第2段階</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G59" s="13" t="inlineStr">
@@ -9229,26 +9379,26 @@
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>広域連合・3町</t>
+          <t>美瑛町</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の6事業別の事業費</t>
+          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第3節2 令和8年9月25日受領資料の受領点検</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -9274,21 +9424,21 @@
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>東川町</t>
+          <t>東神楽町</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座の開催回数・修了者数</t>
+          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -9319,31 +9469,31 @@
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>美瑛町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入に係る取組の内容</t>
+          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G62" s="13" t="inlineStr">
@@ -9364,31 +9514,31 @@
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>東神楽町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>認知症サポーター養成講座及びステップアップ講座の開催回数・修了者数</t>
+          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G63" s="13" t="inlineStr">
@@ -9409,31 +9559,31 @@
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・法令</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>介護保険事務システムの標準化対応・改修・データ移行の予定</t>
+          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G64" s="13" t="inlineStr">
@@ -9454,31 +9604,31 @@
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携の北海道における実施の方針</t>
+          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
@@ -9499,26 +9649,26 @@
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>3町・法令</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画（計画書）と老人福祉法第20条の8の条文</t>
+          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第8節 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -9544,31 +9694,31 @@
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>3町・事業者</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する基本的な計画の策定の状況、中核機関の整備の状況</t>
+          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標1 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
@@ -9589,31 +9739,31 @@
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>北海道・国の政令</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>地域防災計画に定める要配慮者利用施設の一覧、避難確保計画の作成及び避難訓練の実施の状況</t>
+          <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第5章 基本目標5 計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節 サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
@@ -9632,98 +9782,8 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="40" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>184</v>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>3町・事業者</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>積雪期のみ利用する方の人数及び31日以上連続して利用する方の人数（令和7年度）</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節 注1-1・第6章第4節 サービス見込量の算定（季節補正）</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>通常（0点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="40" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>186</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>特定施設の定義の改正による区域内3施設の扱い</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>北海道・国の政令</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>区域内3施設が登録有料老人ホームの登録を受けることとなるか</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節 サービス見込量の算定（施設・居住系サービス）</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>通常（0点）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="70" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69" ht="70" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>注1　影響度は、期限、止めている成果物、保険料の月額への効き、法定記載事項であるかどうか、及び決着しない場合の扱いの有無により点を付けたものです。9点以上を至急、6点から8点を優先としています。
 注2　月額への効きは、当該の前提のみを動かした場合の保険料基準額（月額）の変化です。
@@ -9735,7 +9795,7 @@
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A69:I69"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9747,7 +9807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -9763,7 +9823,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分A　資料が届かない場合の扱い（66件）</t>
+          <t>区分A　資料が届かない場合の扱い（64件）</t>
         </is>
       </c>
     </row>
@@ -12053,78 +12113,8 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>192</v>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>④　現に確認できている値で確定する</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="104" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="69" ht="104" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>注1　扱いの区分は 01シート の3によります。①安全側の置き方で算定する、②未確定箇所として残す、③当該の記載を掲げない（算定しない）、④現に確認できている値で確定する、の4つです。
 注2　「代替の出どころ」は、当方の扱いが依っている資料です。公表資料・年報・北海道の名簿・3町の実施報告書・既に受領している資料のいずれかによるものを示しています。
@@ -12135,8 +12125,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12149,7 +12139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12165,7 +12155,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分B・B待　公表資料により確認できるもの（7件）・公表を待つもの（3件）</t>
+          <t>区分B・B待　公表資料により確認できるもの（6件）・公表を待つもの（3件）</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12170,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　公表済みのもの（区分B　7件）</t>
+          <t>1　公表済みのもの（区分B　6件）</t>
         </is>
       </c>
     </row>
@@ -12308,31 +12298,31 @@
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>法令・国の計画・北海道の計画</t>
+          <t>国の公表資料</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文、国の認知症施策推進基本計画、北海道の認知症施策推進計画の策定状況</t>
+          <t>介護給付費分科会の資料のうちなお受領していないもの</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2 認知症施策推進計画の位置づけと見込量への反映</t>
+          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節 介護給付費分科会の論点整理の受領点検 介護給付費分科会資料（原典）の受領点検</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -12342,37 +12332,37 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の資料（原本）のご提供</t>
+          <t>「特定地域支援事業支援額」の内容</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>国の公表資料</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の資料のうちなお受領していないもの</t>
+          <t>「特定地域支援事業支援額」を定める介護保険法の条文（第123条第4項が引く額の定義）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節 介護給付費分科会の論点整理の受領点検 介護給付費分科会資料（原典）の受領点検</t>
+          <t>計画素案 第1章第9節1・第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
@@ -12382,17 +12372,17 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>「特定地域支援事業支援額」の内容</t>
+          <t>地域支援事業費の政令で定める額</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -12402,12 +12392,12 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>「特定地域支援事業支援額」を定める介護保険法の条文（第123条第4項が引く額の定義）</t>
+          <t>介護保険法施行令のうち地域支援事業に要する費用の額の上限を定める規定（法第115条の45第4項）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節1・第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
+          <t>計画素案 第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -12417,22 +12407,22 @@
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
+          <t>令和6年度決算の水準を据え置いたまま算定し、政令で定める額との関係を確かめていない旨を計画素案の注に［要確認］として記載する</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -12442,17 +12432,17 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>介護保険法施行令のうち地域支援事業に要する費用の額の上限を定める規定（法第115条の45第4項）</t>
+          <t>医療法等の一部を改正する法律（令和7年法律第87号）による介護保険法の改正の内容及び施行の日、並びに医療法第30条の18の5の条文</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
+          <t>計画素案 第1章第8節・第1章第9節1・第1章第9節6</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -12462,127 +12452,127 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算の水準を据え置いたまま算定し、政令で定める額との関係を確かめていない旨を計画素案の注に［要確認］として記載する</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>法令</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>医療法等の一部を改正する法律（令和7年法律第87号）による介護保険法の改正の内容及び施行の日、並びに医療法第30条の18の5の条文</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第1章第8節・第1章第9節1・第1章第9節6</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
+          <t>医療との連携は第5章 基本目標1及び第6章第5節の記述により扱い、医療法の協議の結果の考慮については施行の時期を確認できていない旨を［要確認］として記載する</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　公表を待つもの（区分B待　3件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>公表の主体</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>待っているもの</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>止めている成果物</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>公表されるまでの当方の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>第10期の政令改正の内容（所得段階）</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>国の政令</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>第10期の標準段階数・標準乗率・公費軽減の乗率・第1号被保険者負担割合</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>第10期の段階設計 保険料の算定</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>医療との連携は第5章 基本目標1及び第6章第5節の記述により扱い、医療法の協議の結果の考慮については施行の時期を確認できていない旨を［要確認］として記載する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>2　公表を待つもの（区分B待　3件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>公表の主体</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>待っているもの</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>止めている成果物</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>公表されるまでの当方の扱い</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
-          <t>国の政令</t>
+          <t>国の公表資料</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>第10期の標準段階数・標準乗率・公費軽減の乗率・第1号被保険者負担割合</t>
+          <t>介護サービス事業者経営情報データベースの分析結果（令和9年4月以降に公表される予定）</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計 保険料の算定</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -12592,37 +12582,37 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>国の公表資料</t>
+          <t>国の省令</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの分析結果（令和9年4月以降に公表される予定）</t>
+          <t>小規模市町村の基準（厚生労働省令）</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
+          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -12632,111 +12622,103 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>185</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>国の省令</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>小規模市町村の基準（厚生労働省令）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節 サービス見込量の算定（地域支援事業費）</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>3　区分Cのうち、公表を待つ要素を含むもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>待っているもの</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>状態</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>公表されるまでの当方の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>国の政令・省令</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>3　区分Cのうち、公表を待つ要素を含むもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>待っているもの</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>状態</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>公表されるまでの当方の扱い</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>国の政令・省令</t>
+          <t>国の告示</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
@@ -12746,45 +12728,13 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>183</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>国の告示</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
-        <is>
-          <t>受託者案で確定（告示後に再算定）</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
           <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25" ht="86" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="23"/>
+    <row r="24" ht="86" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>注1　当方の作業環境は、厚生労働省、政府統計の総合窓口、北海道、介護保険地域包括ケア「見える化」システム及び介護サービス情報公表システムのいずれにも接続できません。このため、公表資料であっても写しのご提供をお願いすることになります。
 注2　公表を待つものは、国の政令・省令・告示その他によるもので、ご提供の催促ができるものではありません。いずれも現行の制度により算定し、公布又は告示の後に再算定する扱いとしています。
@@ -12795,10 +12745,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12811,7 +12761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -12828,7 +12778,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分C　ご判断・ご決定を求めるもの（96件）</t>
+          <t>区分C　ご判断・ご決定を求めるもの（97件）</t>
         </is>
       </c>
     </row>
@@ -12889,16 +12839,16 @@
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="5" t="n">
-        <v>3</v>
+        <v>193</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>都道府県へ推計データを提出する際に入力する「改正介護保険法を踏まえた第10期計画の策定における取組」の回答</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>類似保険者の選定条件と比較対象の保険者</t>
+          <t>都道府県へ推計データを提出する際に入力する「改正介護保険法を踏まえた第10期計画策定における取組」（3群8問）の回答。中長期的な推計を定めた年度の選択肢に令和17年度がないこと、及び現に実施された検討・分析・協議の状況によるものであり受託者が代わって判断できないことによる</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -12908,17 +12858,17 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節 分析資料</t>
+          <t>計画素案 第6章第1節・第6章第3節2・第6章第4節1・第6章第5節 見える化システムへの入力</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
@@ -12928,22 +12878,22 @@
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>通常（0点）</t>
+          <t>通常（1点）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16を代理指標へ振り替えるかどうか</t>
+          <t>類似保険者の選定条件と比較対象の保険者</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -12953,12 +12903,12 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・資料1 全16KPIの4項目</t>
+          <t>素案 第2章第2節 分析資料</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -12979,26 +12929,26 @@
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項（重大6件）の取扱いと、事業所への照会の要否</t>
+          <t>代表KPI H07・H08・H12・H16を代理指標へ振り替えるかどうか</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第5・6節 H06・H11・H13・H14の基準値</t>
+          <t>素案 第4章第3節・資料1 全16KPIの4項目</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -13024,31 +12974,31 @@
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列（社人研推計か3町の総合計画か）</t>
+          <t>3調査の点検事項（重大6件）の取扱いと、事業所への照会の要否</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 将来推計</t>
+          <t>素案 第2章第5・6節 H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -13069,16 +13019,16 @@
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>3町の第10期計画へ共通指標を掲載することの合意</t>
+          <t>人口推計の基礎とする系列（社人研推計か3町の総合計画か）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -13088,7 +13038,7 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2 3町協議資料</t>
+          <t>素案 第6章第1節 将来推計</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
@@ -13114,16 +13064,16 @@
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>骨子案（章立て・基本理念・基本目標・代表KPIの枠組み）</t>
+          <t>3町の第10期計画へ共通指標を掲載することの合意</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -13133,7 +13083,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>骨子案 素案の次稿</t>
+          <t>素案 資料2 3町協議資料</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -13159,31 +13109,31 @@
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>策定委員会の開催日程・審議事項・資料提出期限、意見公募手続の期間、町別値の公表基準</t>
+          <t>骨子案（章立て・基本理念・基本目標・代表KPIの枠組み）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>委員会資料原案 パブリックコメント資料</t>
+          <t>骨子案 素案の次稿</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G11" s="13" t="inlineStr">
@@ -13204,31 +13154,31 @@
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様（章別の頁配分・図表の掲載点数・概要版・入稿期限）</t>
+          <t>策定委員会の開催日程・審議事項・資料提出期限、意見公募手続の期間、町別値の公表基準</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部） 概要版</t>
+          <t>委員会資料原案 パブリックコメント資料</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G12" s="13" t="inlineStr">
@@ -13249,31 +13199,31 @@
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標のうち「市町村数」を単位とするものの読替えの考え方</t>
+          <t>成果品の仕様（章別の頁配分・図表の掲載点数・概要版・入稿期限）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（北海道）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節 追加調査報告書 04シート</t>
+          <t>計画書（印刷200部） 概要版</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G13" s="13" t="inlineStr">
@@ -13294,31 +13244,31 @@
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策（4案のいずれか）</t>
+          <t>北海道の評価指標のうち「市町村数」を単位とするものの読替えの考え方</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（北海道）</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節 見込量表（3種別）</t>
+          <t>素案 第1章第6節 追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="F14" s="13" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G14" s="13" t="inlineStr">
@@ -13339,16 +13289,16 @@
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの目標値の決定</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの令和11年度目標値</t>
+          <t>24時間対応サービスの確保方策（4案のいずれか）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -13358,7 +13308,7 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・第5章 全16KPIの目標値</t>
+          <t>素案 第6章第2節・第4節 見込量表（3種別）</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -13384,16 +13334,16 @@
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>各調査の対象者の範囲（母集団が異なる指標を併記する前提）</t>
+          <t>代表KPIの令和11年度目標値</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -13403,12 +13353,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート H06・H11の基準値</t>
+          <t>素案 第4章第3節・第5章 全16KPIの目標値</t>
         </is>
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -13429,16 +13379,16 @@
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提（3案のいずれか）</t>
+          <t>各調査の対象者の範囲（母集団が異なる指標を併記する前提）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -13448,12 +13398,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節 認定者数・給付費の推計</t>
+          <t>調査クロス集計・分析 13・14シート H06・H11の基準値</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -13474,16 +13424,16 @@
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>給付適正化を第10期に実施するか、推計へ政策効果として見込むか</t>
+          <t>重度化の速度の前提（3案のいずれか）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -13493,7 +13443,7 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章 給付費の推計</t>
+          <t>素案 第6章第1節 認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
@@ -13519,16 +13469,16 @@
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案の内容</t>
+          <t>給付適正化を第10期に実施するか、推計へ政策効果として見込むか</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -13538,12 +13488,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>計画骨子案 施策体系新旧対照表 計画素案 第4章・第5章</t>
+          <t>素案 第6章第2節・第5章・第7章 給付費の推計</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
@@ -13564,26 +13514,26 @@
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数を延べとするか施設単位の実人数とするか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案の内容</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>従業員数の重複計上の整理 計画素案 第2章第3節・第6章第2節</t>
+          <t>計画骨子案 施策体系新旧対照表 計画素案 第4章・第5章</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -13609,26 +13559,26 @@
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数を第9期の評価・第10期の課題として扱うか</t>
+          <t>社会資源一覧の従業員数を延べとするか施設単位の実人数とするか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>中間報告 第3節 計画素案 第2章・第5章</t>
+          <t>従業員数の重複計上の整理 計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -13654,16 +13604,16 @@
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母（標準給付費見込額か総給付費か）</t>
+          <t>認定に要する日数を第9期の評価・第10期の課題として扱うか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -13673,7 +13623,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章 資料1 中間報告 第3節</t>
+          <t>中間報告 第3節 計画素案 第2章・第5章</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -13699,16 +13649,16 @@
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ3件の確認</t>
+          <t>代表KPI H15の分母（標準給付費見込額か総給付費か）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -13718,7 +13668,7 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>計画素案 第4章 資料1 中間報告 第3節</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
@@ -13744,26 +13694,26 @@
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基金の積立ての上限の解釈と第10期の取崩方針</t>
+          <t>月報の値の接続のずれ3件の確認</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認 02シート 素案 第6章第6節 将来推計 第3段階</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="F24" s="13" t="inlineStr">
@@ -13789,26 +13739,26 @@
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティから個人情報を削除する運用</t>
+          <t>基金の積立ての上限の解釈と第10期の取崩方針</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録 業務工程管理表</t>
+          <t>基金条例の確認 02シート 素案 第6章第6節 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F25" s="13" t="inlineStr">
@@ -13834,16 +13784,16 @@
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>議事録の文書プロパティから個人情報を削除する運用</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -13879,16 +13829,16 @@
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービス2件の第10期の計画値の置き方</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -13898,7 +13848,7 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
+          <t>中間報告会議議事録 業務工程管理表</t>
         </is>
       </c>
       <c r="F27" s="13" t="inlineStr">
@@ -13924,16 +13874,16 @@
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎に包括的支援事業費・任意事業費を含めない扱い</t>
+          <t>計画値を0としたサービス2件の第10期の計画値の置き方</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -13943,7 +13893,7 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>見える化総括表の受領点検 02シート 計画素案 第4章</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -13969,16 +13919,16 @@
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提4件</t>
+          <t>調整交付金の算定基礎に包括的支援事業費・任意事業費を含めない扱い</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -13988,7 +13938,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート 計画素案 第6章第6節</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="F29" s="13" t="inlineStr">
@@ -13998,7 +13948,7 @@
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H29" s="13" t="inlineStr">
@@ -14014,16 +13964,16 @@
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の保険料算定の前提4件</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -14033,7 +13983,7 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>将来推計 第3段階 05・06シート 計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -14043,7 +13993,7 @@
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H30" s="13" t="inlineStr">
@@ -14059,16 +14009,16 @@
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を地方創生総合戦略とすること（案C）</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -14078,7 +14028,7 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎の変更_総合戦略ベース 将来推計 第1〜3段階 計画素案 第2章第1節・第6章</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
@@ -14104,16 +14054,16 @@
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>人口推計の基礎を地方創生総合戦略とすること（案C）</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -14123,7 +14073,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案 計画素案 第6章第4節</t>
+          <t>人口推計の基礎の変更_総合戦略ベース 将来推計 第1〜3段階 計画素案 第2章第1節・第6章</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
@@ -14149,16 +14099,16 @@
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -14168,7 +14118,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位 介護高齢者福祉サービスガイド_構成案 計画素案 第5章・第6章第3節2</t>
+          <t>介護高齢者福祉サービスガイド_構成案 計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="F33" s="13" t="inlineStr">
@@ -14194,16 +14144,16 @@
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="5" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果2件）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -14213,7 +14163,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>算定方法の整合確認（国と見える化） 将来推計 第2段階・第3段階 計画素案 第6章第3節・第6節</t>
+          <t>広域連合において行うべき事業の優先順位 介護高齢者福祉サービスガイド_構成案 計画素案 第5章・第6章第3節2</t>
         </is>
       </c>
       <c r="F34" s="13" t="inlineStr">
@@ -14239,31 +14189,31 @@
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応、3町の該当状況調査の回答</t>
+          <t>算定方法の国の様式との整合（点検結果2件）</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>算定方法の整合確認（国と見える化） 将来推計 第2段階・第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G35" s="13" t="inlineStr">
@@ -14284,26 +14234,26 @@
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位を計画本文に掲げるか</t>
+          <t>成果指向型配分枠への対応、3町の該当状況調査の回答</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（3町）</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第4節 図表集 27シート 交付金評価指標と全国集計の受領点検 04シート</t>
+          <t>計画素案 第5章 交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -14329,16 +14279,16 @@
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="5" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと「第10期へ引き継ぐ改善事項」の再整理案</t>
+          <t>交付金の全国順位を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -14348,7 +14298,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章・資料1 骨子案 第4節 図表集31シート 代表KPIの振替案と確認事項の精査</t>
+          <t>計画素案 第3章第4節 図表集 27シート 交付金評価指標と全国集計の受領点検 04シート</t>
         </is>
       </c>
       <c r="F37" s="13" t="inlineStr">
@@ -14374,16 +14324,16 @@
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="5" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策の数にも簡素化の考え方を及ぼすか</t>
+          <t>代表KPIと「第10期へ引き継ぐ改善事項」の再整理案</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -14393,7 +14343,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 骨子案 第5節</t>
+          <t>計画素案 第4章第3節・第5章・資料1 骨子案 第4節 図表集31シート 代表KPIの振替案と確認事項の精査</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -14419,16 +14369,16 @@
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複の確認を行うか</t>
+          <t>第5章の施策の数にも簡素化の考え方を及ぼすか</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -14438,7 +14388,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08 実施済み3調査の受領点検と集計 06・07</t>
+          <t>計画素案 第5章 骨子案 第5節</t>
         </is>
       </c>
       <c r="F39" s="13" t="inlineStr">
@@ -14464,16 +14414,16 @@
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="5" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法</t>
+          <t>職員個票のリストによる重複の確認を行うか</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -14483,7 +14433,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料 町別データシート 構成町の意見への回答 2・3</t>
+          <t>内部確認結果への対応整理 03・08 実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
@@ -14509,26 +14459,26 @@
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="5" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針（4件）</t>
+          <t>構成町との意見交換会の実施方法</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東川町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第2章第2節・第6章第2節・第4節 構成町の意見への回答 6</t>
+          <t>意見交換会資料 町別データシート 構成町の意見への回答 2・3</t>
         </is>
       </c>
       <c r="F41" s="13" t="inlineStr">
@@ -14554,26 +14504,26 @@
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>東川町の施設整備・サービス提供方針（4件）</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東川町）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>町別データシート 構成町の意見への回答 2</t>
+          <t>サービス見込量 第2次概算 計画素案 第2章第2節・第6章第2節・第4節 構成町の意見への回答 6</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -14599,16 +14549,16 @@
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>交付金の交付見込額を保険料収納必要額から控除するか</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -14618,7 +14568,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第6節 将来推計 第3段階 保険料算定式の国の様式との対照</t>
+          <t>町別データシート 構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
@@ -14644,26 +14594,26 @@
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数の基盤整備単位、認知症対応型共同生活介護の圏域別の定員</t>
+          <t>交付金の交付見込額を保険料収納必要額から控除するか</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第7節・第6章第4節4 サービス見込量の算定</t>
+          <t>計画素案 第6章第6節 将来推計 第3段階 保険料算定式の国の様式との対照</t>
         </is>
       </c>
       <c r="F44" s="13" t="inlineStr">
@@ -14689,26 +14639,26 @@
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律による改正の反映（7件）</t>
+          <t>日常生活圏域ごとの必要利用定員総数の基盤整備単位、認知症対応型共同生活介護の圏域別の定員</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>公表資料により確認できるもの（法令）</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節 ケアプラン点検実施要領</t>
+          <t>計画素案 第1章第7節・第6章第4節4 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr">
@@ -14718,7 +14668,7 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H45" s="13" t="inlineStr">
@@ -14734,26 +14684,26 @@
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="A46" s="5" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案B）の反映内容</t>
+          <t>社会福祉法等の一部を改正する法律による改正の反映（7件）</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>公表資料により確認できるもの（法令）</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標5・資料5 給付適正化計画の位置づけと追加検討事項</t>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節 ケアプラン点検実施要領</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -14763,7 +14713,7 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
@@ -14779,26 +14729,26 @@
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="A47" s="5" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件（協力医療機関の要件・生産性向上の委員会）への対応</t>
+          <t>給付適正化計画の位置づけ（案B）の反映内容</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節 計画素案 第5章 基本目標3・4 計画素案 第6章第4節3</t>
+          <t>計画素案 第1章第2節・第5章 基本目標5・資料5 給付適正化計画の位置づけと追加検討事項</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr">
@@ -14824,26 +14774,26 @@
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="A48" s="5" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型5件を計画に掲げるか</t>
+          <t>令和9年4月1日から義務となる2件（協力医療機関の要件・生産性向上の委員会）への対応</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節1 計画素案 第6章第2節2（2） サービス見込量の算定</t>
+          <t>計画素案 第1章第9節 計画素案 第5章 基本目標3・4 計画素案 第6章第4節3</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -14869,16 +14819,16 @@
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="5" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>基盤整備の選択肢として省令上の類型5件を計画に掲げるか</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -14888,7 +14838,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節・第3節・第6節</t>
+          <t>計画素案 第6章第4節1 計画素案 第6章第2節2（2） サービス見込量の算定</t>
         </is>
       </c>
       <c r="F49" s="13" t="inlineStr">
@@ -14914,16 +14864,16 @@
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="5" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の見込量の表の数値の差し替え</t>
+          <t>見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -14933,7 +14883,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2 サービス見込量の算定</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節・第3節・第6節</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr">
@@ -14959,16 +14909,16 @@
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="5" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>計画素案 第6章第2節の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -14978,7 +14928,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
+          <t>計画素案 第6章第2節2 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr">
@@ -15004,16 +14954,16 @@
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="5" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -15023,7 +14973,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -15033,7 +14983,7 @@
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H52" s="13" t="inlineStr">
@@ -15049,16 +14999,16 @@
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="5" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -15068,7 +15018,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第4章第3節・第6章第2節</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr">
@@ -15078,12 +15028,12 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>最大13円</t>
+          <t>受託者案で確定（告示後に再算定）</t>
+        </is>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
@@ -15094,16 +15044,16 @@
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="5" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びにサービス別の趨勢を半分反映するか</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -15113,7 +15063,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
+          <t>サービス見込量の算定 計画素案 第4章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -15128,7 +15078,7 @@
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>最大58円</t>
+          <t>最大13円</t>
         </is>
       </c>
       <c r="I54" s="13" t="inlineStr">
@@ -15139,26 +15089,26 @@
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="5" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>施設及び居住系の実績の減少を将来へ延長するか</t>
+          <t>見込量の伸びにサービス別の趨勢を半分反映するか</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第4節4</t>
+          <t>サービス見込量の算定 将来推計 第3段階 計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr">
@@ -15171,9 +15121,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>最大58円</t>
         </is>
       </c>
       <c r="I55" s="13" t="inlineStr">
@@ -15184,26 +15134,26 @@
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="5" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>施設及び居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（3町）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
+          <t>サービス見込量の算定 計画素案 第6章第4節4</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
@@ -15213,7 +15163,7 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
@@ -15229,16 +15179,16 @@
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="5" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないこと</t>
+          <t>単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -15248,7 +15198,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第5章 基本目標5・第6章第2節</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr">
@@ -15258,12 +15208,12 @@
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-      <c r="H57" s="7" t="inlineStr">
-        <is>
-          <t>最大327円</t>
+          <t>受託者案で確定（告示後に再算定）</t>
+        </is>
+      </c>
+      <c r="H57" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
@@ -15274,26 +15224,26 @@
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因12件の扱い</t>
+          <t>給付適正化の効果を見込量に織り込まないこと</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（3町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>サービス見込量の算定 計画素案 第5章 基本目標5・第6章第2節</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -15306,9 +15256,9 @@
           <t>受託者案で確定</t>
         </is>
       </c>
-      <c r="H58" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="I58" s="13" t="inlineStr">
@@ -15319,26 +15269,26 @@
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="5" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>中長期推計をどこまで算定し、どこまで計画本文に掲げるか</t>
+          <t>過年度の趨勢に現れない要因12件の扱い</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（3町）</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第2章第8節・第6章第2節</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr">
@@ -15364,26 +15314,26 @@
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="5" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される3区分を見込量に立てるか</t>
+          <t>中長期推計をどこまで算定し、どこまで計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>公表を待つもの（国の政令・省令）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第1章第9節・第6章第2節・第4節</t>
+          <t>サービス見込量 第2次概算 将来推計 第3段階 計画素案 第2章第8節・第6章第2節</t>
         </is>
       </c>
       <c r="F60" s="13" t="inlineStr">
@@ -15393,7 +15343,7 @@
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
+          <t>受託者案で確定</t>
         </is>
       </c>
       <c r="H60" s="13" t="inlineStr">
@@ -15409,26 +15359,26 @@
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="5" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>令和9年4月に新設される3区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
+          <t>公表を待つもの（国の政令・省令）</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第6章第2節・第4節</t>
+          <t>サービス見込量 第2次概算 計画素案 第1章第9節・第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F61" s="13" t="inlineStr">
@@ -15438,7 +15388,7 @@
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="H61" s="13" t="inlineStr">
@@ -15454,26 +15404,26 @@
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="5" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合・3町）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧 送付資料一覧</t>
+          <t>サービス見込量 第2次概算 計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
@@ -15499,16 +15449,16 @@
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="5" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを施策化への転換率とするか</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -15518,7 +15468,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
+          <t>成果品一覧 送付資料一覧</t>
         </is>
       </c>
       <c r="F63" s="13" t="inlineStr">
@@ -15544,16 +15494,16 @@
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式</t>
+          <t>施策2-5の代表KPIを施策化への転換率とするか</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -15563,7 +15513,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2 第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="F64" s="13" t="inlineStr">
@@ -15589,16 +15539,16 @@
     </row>
     <row r="65" ht="36" customHeight="1">
       <c r="A65" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>地域ケア会議の3町共通の記録様式</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -15608,7 +15558,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
@@ -15634,16 +15584,16 @@
     </row>
     <row r="66" ht="36" customHeight="1">
       <c r="A66" s="5" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料（転載を禁ずる記載のある2件）の取扱い</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -15653,7 +15603,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の受領点検とKPI設計案 計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
@@ -15679,16 +15629,16 @@
     </row>
     <row r="67" ht="36" customHeight="1">
       <c r="A67" s="5" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式を基本推計とするか</t>
+          <t>地域ケア会議関係資料（転載を禁ずる記載のある2件）の取扱い</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -15698,7 +15648,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>地域ケア会議の受領点検とKPI設計案 計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
@@ -15724,26 +15674,26 @@
     </row>
     <row r="68" ht="36" customHeight="1">
       <c r="A68" s="5" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>見える化システムの推計方式を基本推計とするか</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合（システムの操作））</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階 計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
@@ -15769,26 +15719,26 @@
     </row>
     <row r="69" ht="36" customHeight="1">
       <c r="A69" s="5" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合（システムの操作））</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>将来推計 第1段階 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
@@ -15814,16 +15764,16 @@
     </row>
     <row r="70" ht="36" customHeight="1">
       <c r="A70" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>利用率等の伸びの選択（4つの選択肢のいずれか）</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -15859,16 +15809,16 @@
     </row>
     <row r="71" ht="36" customHeight="1">
       <c r="A71" s="5" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画の扱い</t>
+          <t>利用率等の伸びの選択（4つの選択肢のいずれか）</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -15878,7 +15828,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F71" s="13" t="inlineStr">
@@ -15904,16 +15854,16 @@
     </row>
     <row r="72" ht="36" customHeight="1">
       <c r="A72" s="5" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画の扱い</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -15923,7 +15873,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節・第3節 サービス見込量の算定</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="F72" s="13" t="inlineStr">
@@ -15949,16 +15899,16 @@
     </row>
     <row r="73" ht="36" customHeight="1">
       <c r="A73" s="5" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -15968,7 +15918,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階 サービス見込量の算定</t>
+          <t>計画素案 第6章第2節・第3節 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F73" s="13" t="inlineStr">
@@ -15978,12 +15928,12 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定（告示後に再算定）</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>最大327円</t>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
         </is>
       </c>
       <c r="I73" s="13" t="inlineStr">
@@ -15994,26 +15944,26 @@
     </row>
     <row r="74" ht="36" customHeight="1">
       <c r="A74" s="5" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>将来推計 第2段階 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F74" s="13" t="inlineStr">
@@ -16023,12 +15973,12 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>受託者案で確定</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
+          <t>受託者案で確定（告示後に再算定）</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>最大327円</t>
         </is>
       </c>
       <c r="I74" s="13" t="inlineStr">
@@ -16039,26 +15989,26 @@
     </row>
     <row r="75" ht="36" customHeight="1">
       <c r="A75" s="5" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第4節・第4章第3節</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
@@ -16084,26 +16034,26 @@
     </row>
     <row r="76" ht="36" customHeight="1">
       <c r="A76" s="5" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い、区域外利用の把握の手段</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節4 サービス見込量の算定</t>
+          <t>計画素案 第2章第4節・第4章第3節</t>
         </is>
       </c>
       <c r="F76" s="13" t="inlineStr">
@@ -16129,26 +16079,26 @@
     </row>
     <row r="77" ht="36" customHeight="1">
       <c r="A77" s="5" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>概算を既定値のまま出してよいか</t>
+          <t>区域を越えた施設利用の扱い、区域外利用の把握の手段</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（広域連合）</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>計画素案 第6章第4節4 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F77" s="13" t="inlineStr">
@@ -16174,16 +16124,16 @@
     </row>
     <row r="78" ht="36" customHeight="1">
       <c r="A78" s="5" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -16193,7 +16143,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="F78" s="13" t="inlineStr">
@@ -16219,16 +16169,16 @@
     </row>
     <row r="79" ht="36" customHeight="1">
       <c r="A79" s="5" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -16238,7 +16188,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr">
@@ -16264,16 +16214,16 @@
     </row>
     <row r="80" ht="36" customHeight="1">
       <c r="A80" s="5" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -16283,7 +16233,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>町別データシート サービス見込量の算定</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="F80" s="13" t="inlineStr">
@@ -16309,16 +16259,16 @@
     </row>
     <row r="81" ht="36" customHeight="1">
       <c r="A81" s="5" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -16328,7 +16278,7 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+          <t>町別データシート サービス見込量の算定</t>
         </is>
       </c>
       <c r="F81" s="13" t="inlineStr">
@@ -16354,16 +16304,16 @@
     </row>
     <row r="82" ht="36" customHeight="1">
       <c r="A82" s="5" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -16373,7 +16323,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 サービス見込量の算定</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
@@ -16399,16 +16349,16 @@
     </row>
     <row r="83" ht="36" customHeight="1">
       <c r="A83" s="5" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外すか</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -16418,7 +16368,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+          <t>見える化システムへの入力 サービス見込量の算定</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
@@ -16444,16 +16394,16 @@
     </row>
     <row r="84" ht="36" customHeight="1">
       <c r="A84" s="5" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外すか</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -16463,12 +16413,12 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
@@ -16489,16 +16439,16 @@
     </row>
     <row r="85" ht="36" customHeight="1">
       <c r="A85" s="5" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cから変化率法に改めるか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -16534,16 +16484,16 @@
     </row>
     <row r="86" ht="36" customHeight="1">
       <c r="A86" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>人口の将来推計の方法を案Cから変化率法に改めるか</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -16553,7 +16503,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節 図表集</t>
+          <t>サービス見込量 第2次概算 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="F86" s="13" t="inlineStr">
@@ -16579,16 +16529,16 @@
     </row>
     <row r="87" ht="36" customHeight="1">
       <c r="A87" s="5" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -16598,7 +16548,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標3・資料1 アンケート調査の集計分析報告書 02・14シート</t>
+          <t>計画素案 第2章第1節 図表集</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
@@ -16624,26 +16574,26 @@
     </row>
     <row r="88" ht="36" customHeight="1">
       <c r="A88" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東川町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1 アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
@@ -16669,26 +16619,26 @@
     </row>
     <row r="89" ht="36" customHeight="1">
       <c r="A89" s="5" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけと3町展開</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東川町）</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
@@ -16714,21 +16664,21 @@
     </row>
     <row r="90" ht="36" customHeight="1">
       <c r="A90" s="5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>東川町のチームオレンジ事業の位置づけと3町展開</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（美瑛町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
@@ -16759,21 +16709,21 @@
     </row>
     <row r="91" ht="36" customHeight="1">
       <c r="A91" s="5" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（美瑛町）</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
@@ -16804,16 +16754,16 @@
     </row>
     <row r="92" ht="36" customHeight="1">
       <c r="A92" s="5" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -16823,7 +16773,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F92" s="13" t="inlineStr">
@@ -16849,26 +16799,26 @@
     </row>
     <row r="93" ht="36" customHeight="1">
       <c r="A93" s="5" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持と担い手の高齢化の状況</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>広域連合から資料の徴求を要するもの（東神楽町）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第6章第4節・第6章第5節 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F93" s="13" t="inlineStr">
@@ -16894,31 +16844,31 @@
     </row>
     <row r="94" ht="36" customHeight="1">
       <c r="A94" s="5" t="n">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>東神楽町の通いの場の維持と担い手の高齢化の状況</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>広域連合から資料の徴求を要するもの（東神楽町）</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート 10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
@@ -16939,16 +16889,16 @@
     </row>
     <row r="95" ht="36" customHeight="1">
       <c r="A95" s="5" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち協議用へ移すもの</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -16958,7 +16908,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート 計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
@@ -16984,16 +16934,16 @@
     </row>
     <row r="96" ht="36" customHeight="1">
       <c r="A96" s="5" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁6件と資料編の構成</t>
+          <t>計画素案に独自に加えた記載のうち協議用へ移すもの</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -17003,7 +16953,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 08シート 計画素案 全体</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート 計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="F96" s="13" t="inlineStr">
@@ -17029,16 +16979,16 @@
     </row>
     <row r="97" ht="36" customHeight="1">
       <c r="A97" s="5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価を示す図3点を計画本文に掲げるか</t>
+          <t>第9期計画にない体裁6件と資料編の構成</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -17048,12 +16998,12 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート 計画素案 第3章第4節・資料7</t>
+          <t>計画素案の記載内容の洗い出しと対比 08シート 計画素案 全体</t>
         </is>
       </c>
       <c r="F97" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G97" s="13" t="inlineStr">
@@ -17074,16 +17024,16 @@
     </row>
     <row r="98" ht="36" customHeight="1">
       <c r="A98" s="5" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応</t>
+          <t>交付金の評価を示す図3点を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
@@ -17093,7 +17043,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート 計画素案 資料7／別冊の図表集</t>
+          <t>図表データ管理台帳 03シート 計画素案 第3章第4節・資料7</t>
         </is>
       </c>
       <c r="F98" s="13" t="inlineStr">
@@ -17119,16 +17069,16 @@
     </row>
     <row r="99" ht="36" customHeight="1">
       <c r="A99" s="5" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか</t>
+          <t>計画本文の図と別冊の図表集の対応</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
@@ -17138,7 +17088,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証 07シート 見える化へ入力する箇所と入力値 02シート 計画素案 第2章第1節・第6章第1節</t>
+          <t>図表データ管理台帳 01シート・02シート 計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
@@ -17164,51 +17114,96 @@
     </row>
     <row r="100" ht="36" customHeight="1">
       <c r="A100" s="5" t="n">
+        <v>174</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>人口推計コーホート分析の妥当性検証 07シート 見える化へ入力する箇所と入力値 02シート 計画素案 第2章第1節・第6章第1節</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="H100" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>通常（0点）</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="5" t="n">
         <v>183</v>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>夜間対応型訪問介護の経過措置の期限と見込量の区分の扱い</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>公表を待つもの（国の告示）</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>計画素案 第6章第2節（2）・第6章第4節1 サービス見込量の算定・見える化システムへの入力値</t>
         </is>
       </c>
-      <c r="F100" s="13" t="inlineStr">
+      <c r="F101" s="13" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G100" s="13" t="inlineStr">
+      <c r="G101" s="13" t="inlineStr">
         <is>
           <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
-      <c r="H100" s="13" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
         <is>
           <t>通常（0点）</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="70" customHeight="1">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102" ht="70" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>注1　ご判断をいただかなくても算定は止まりません。全件に決着しない場合の扱い（既定値）を置いているためです。既定値は 04シート 及び業務工程管理表 03 確認事項一覧の回答欄に掲げています。
 注2　既定値は協議を進めるための仮置きであり、公表の確定の根拠にはなりません。
@@ -17219,8 +17214,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A101:I101"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A102:I102"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17232,7 +17227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -17248,7 +17243,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>区分D　資料の徴求を要しないもの（20件）</t>
+          <t>区分D　資料の徴求を要しないもの（23件）</t>
         </is>
       </c>
     </row>
@@ -17825,46 +17820,46 @@
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>全国自治体共通版の入力シート・手順書を本件に用いるか</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>当方の作業</t>
+          <t>法令・国の計画・北海道の計画</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>全国自治体共通版を本件に用いないこと（了承）</t>
+          <t>認知症基本法の条文（原典により確認済み）、国の認知症施策推進基本計画（令和6年12月3日 閣議決定。原典により確認済み）、北海道の認知症施策推進計画（第10期計画に一体のものとして策定されることを確認済み）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 サービス見込量 第2次概算</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2 認知症施策推進計画の位置づけと見込量への反映</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G20" s="18" t="inlineStr">
         <is>
-          <t>了承済</t>
+          <t>解決</t>
         </is>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>全国自治体共通版の入力シート・手順書を本件に用いるか</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -17874,12 +17869,12 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来推計（ご指示により算定した）</t>
+          <t>全国自治体共通版を本件に用いないこと（了承）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 将来推計 第3段階</t>
+          <t>見える化システムへの入力 サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
@@ -17887,19 +17882,19 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>受託者案で確定</t>
+      <c r="G21" s="18" t="inlineStr">
+        <is>
+          <t>了承済</t>
         </is>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -17909,12 +17904,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>中長期推計の年次を広げること（ご指示により算定した）</t>
+          <t>所得段階別第1号被保険者数の将来推計（ご指示により算定した）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力 計画素案 第6章第1節・第3節</t>
+          <t>見える化システムへの入力 将来推計 第3段階</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -17930,85 +17925,190 @@
     </row>
     <row r="23" ht="34" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較と団体名の扱い</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>国の公表資料</t>
+          <t>当方の作業</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>同様の構成の団体との比較（全国集計結果の原本により解決）</t>
+          <t>中長期推計の年次を広げること（ご指示により算定した）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 06シート</t>
+          <t>見える化システムへの入力 計画素案 第6章第1節・第3節</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G23" s="18" t="inlineStr">
-        <is>
-          <t>解決</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>受託者案で確定</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
       <c r="A24" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>同様の構成の団体との比較と団体名の扱い</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>国の公表資料</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>同様の構成の団体との比較（全国集計結果の原本により解決）</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>交付金評価の取りまとめと第10期への反映 06シート</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="5" t="n">
         <v>181</v>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>介護保険法第117条ほか関係法令の条文のご提供</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>法令</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>参照条文により介護保険法第117条の項の全体（全14項）及び第3項の全10号、第118条並びに第115条の45の項及び号を確認した</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>計画素案 第1章第2節・第1章第5節・第1章第8節・第6章第5節 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G25" s="18" t="inlineStr">
         <is>
           <t>解決</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="52" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>注1　台帳の状態が「解決」「完了」「了承済」となっているものは16件、当方の作業により確認できるものとして本区分に掲げたもののうち台帳の状態がなお「確認待ち」「対応中」であるものは4件です。
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みの算定期間は、地方公共団体向け利用マニュアルにより令和8年5月報告（令和8年3月サービス分）以降と確認済み。本計画は令和7年度（12か月）を基準年度としており影響しない</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定 計画素案 第6章第2節</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="34" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>広域連合</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費は対象経費支出予定額であることを地方公共団体向け利用マニュアルにより確認済み。本計画の額（令和6年度決算の款4による）と範囲が異なることを計画素案 第6章第3節2に注記した</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定 計画素案 第6章第3節2・第6章第6節</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G27" s="18" t="inlineStr">
+        <is>
+          <t>解決</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>注1　台帳の状態が「解決」「完了」「了承済」となっているものは19件、当方の作業により確認できるものとして本区分に掲げたもののうち台帳の状態がなお「確認待ち」「対応中」であるものは4件です。
 注2　後者は、当方の側では決着しているものの、その扱いについてのご確認をお待ちしているものです。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -18022,7 +18122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -19143,95 +19243,80 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="36" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>191</v>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの「介護保険事業状況報告の設定」の画面において、令和8年度の実績見込みの算定に用いる月として設定されている月（起点及び終期）</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>注　②は計画本文に未確定箇所の記号が残るもの、③は当該の事項について記述が残らないものです。①④は資料が届かなくても計画本文を確定でき、当該の事項についての記述も残ります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>5　ご提供をお願いする先ごとの件数</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>お願いする先</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>うち月額に効くもの</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>うち法第117条に関わるもの</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>期限が到来しているもの</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>広域連合</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>③　当該の記載を掲げない（算定しない）</t>
-        </is>
-      </c>
-      <c r="G41" s="18" t="inlineStr">
-        <is>
-          <t>確定できる</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>注　②は計画本文に未確定箇所の記号が残るもの、③は当該の事項について記述が残らないものです。①④は資料が届かなくても計画本文を確定でき、当該の事項についての記述も残ります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="43"/>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>5　ご提供をお願いする先ごとの件数</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="4" t="inlineStr"/>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>お願いする先</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>うち月額に効くもの</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>うち法第117条に関わるもの</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>期限が到来しているもの</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr"/>
+      <c r="C45" s="13" t="n">
+        <v>41</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>39</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1">
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>広域連合</t>
+          <t>広域連合を通じて構成3町</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D46" s="13" t="n">
         <v>1</v>
@@ -19240,92 +19325,72 @@
         <v>3</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて構成3町</t>
+          <t>広域連合を通じて北海道</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて北海道</t>
+          <t>広域連合を通じて国民健康保険団体連合会</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>広域連合を通じて国民健康保険団体連合会</t>
+          <t>広域連合又は構成3町を通じて事業者</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>広域連合又は構成3町を通じて事業者</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52" ht="70" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="50"/>
+    <row r="51" ht="70" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>注1　資料の受領を待たずに算定は進められます。ただし、保険料の月額に効くものは、資料が届いた後に再算定することとなります。
 注2　介護保険法第117条に関わるものは、資料が届かない場合に計画本文へ未確定箇所の記号が残ります。公表の前に解消を要します。
@@ -19337,12 +19402,12 @@
   <mergeCells count="9">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A44:H44"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
